--- a/models/Czech.xlsx
+++ b/models/Czech.xlsx
@@ -8,19 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stanet1\Documents\agroforestreeadvice_vukoz - FULL\agroforestreeadvice_vukoz\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6DD1EB85-D7EE-4BC4-89E8-02E5049190B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27FDACDA-189E-420B-AFD7-7552598A9D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{059DB85A-A06D-4141-92A5-CCF2847AAA02}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{059DB85A-A06D-4141-92A5-CCF2847AAA02}"/>
   </bookViews>
   <sheets>
     <sheet name="dataCzech" sheetId="2" r:id="rId1"/>
     <sheet name="List1" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_1" localSheetId="0" hidden="1">dataCzech!$A$1:$AM$96</definedName>
+    <definedName name="ExternalData_1" localSheetId="0" hidden="1">dataCzech!$A$1:$AM$85</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -49,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2645" uniqueCount="774">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2381" uniqueCount="717">
   <si>
     <t xml:space="preserve">Latin_name                                                  </t>
   </si>
@@ -1458,99 +1457,18 @@
     <t xml:space="preserve">Supplenetary fruit production                                                                                                                                                                                                                                                                                      </t>
   </si>
   <si>
-    <t xml:space="preserve">Cornus mas L.                                                </t>
-  </si>
-  <si>
-    <t xml:space="preserve">dřín jarní - svída dřín                      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">DŘO          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">(2)-(6)   </t>
-  </si>
-  <si>
     <t xml:space="preserve">řezbářství, dekorativní předměty                                                                </t>
   </si>
   <si>
-    <t xml:space="preserve">jedlé plody-marmeláda, želé, mošt, pálenka                                                                                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Funkční, estetický a doplňkově ovocný keř spíše do teplejších oblastí a susší stanoviště                                                                                                                                                                                                                           </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corylus avellana L.                                          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">líska obecná                                 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIO          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">silné pruty-na tyče, jedlé ořechy                                                                                              </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ovocný a funkční keř, menší strom, možno pěstovat výmladkově i v podrostu (zastínění)                                                                                                                                                                                                                              </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mespilus germanica L.                                        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">mišpule obecná                               </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MIN          </t>
-  </si>
-  <si>
     <t xml:space="preserve">(3)-(6)   </t>
   </si>
   <si>
-    <t xml:space="preserve">jedlé plody, džem                                                                                                              </t>
-  </si>
-  <si>
-    <t xml:space="preserve">doplňkově ovocný keř pro teplejší, výsušná i další stanoviště                                                                                                                                                                                                                                                      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ribes spp.                                                   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">rybízy                                       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">RB+          </t>
-  </si>
-  <si>
     <t xml:space="preserve">(1)-(3)   </t>
   </si>
   <si>
     <t xml:space="preserve">shrub               </t>
   </si>
   <si>
-    <t xml:space="preserve">Produkční ovocný keř snášející dobře zastínění                                                                                                                                                                                                                                                                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sambucus nigra L.                                            </t>
-  </si>
-  <si>
-    <t xml:space="preserve">bez černý                                    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BEC          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">( 3)-(8)  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">výroba fujar                                                                                    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">květy-čaj, sirup, plody-víno, nápoje, sirup, větve na slovanské píšťaly "koncovky", zpevňování břehů                       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Funkční, produkční a ovocná dřevina keřového vzrůstu pro bohatá stanoviště                                                                                                                                                                                                                                         </t>
-  </si>
-  <si>
     <t xml:space="preserve">Vaccinium corymbosum L.                                      </t>
   </si>
   <si>
@@ -1590,24 +1508,6 @@
     <t xml:space="preserve">funkční a příp. doplňkove produkční strom pro chladnější oblasti                                                                                                                                                                                                                                                   </t>
   </si>
   <si>
-    <t xml:space="preserve">Berberis vulgaris L.                                         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">dřišťál obecný                               </t>
-  </si>
-  <si>
-    <t xml:space="preserve">DŠO          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">intarzie                                                                                        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">léčivé plody-vitamín C, nápoj, nezralé plody sušené na korálky, léčiva z kůry kmínku a kořenů, listů (nezralé plody jedovaté!) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doplňkově ovocný a estetický keř spíše do teplejších oblastí                                                                                                                                                                                                                                                       </t>
-  </si>
-  <si>
     <t xml:space="preserve">Crataegus monogyna Jacq.                                     </t>
   </si>
   <si>
@@ -1692,21 +1592,6 @@
     <t xml:space="preserve">Skupina domácích přírodních často endemitických mikrodruhů, vhodných pro pěstování v oblasti původu                                                                                                                                                                                                                </t>
   </si>
   <si>
-    <t xml:space="preserve">Viburnum opulus L.                                           </t>
-  </si>
-  <si>
-    <t xml:space="preserve">kalina obecná                                </t>
-  </si>
-  <si>
-    <t xml:space="preserve">KAO          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">nouzově jedlá, hořké plody, sušené jako koření Rusko                                                                           </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doplňková estetická dřevina pro širokou škálu stanovišt                                                                                                                                                                                                                                                            </t>
-  </si>
-  <si>
     <t xml:space="preserve">Cydonia oblonga Mill.                                        </t>
   </si>
   <si>
@@ -1725,39 +1610,6 @@
     <t xml:space="preserve">Menší funkční a eststetický keř na tepleší a sušší stanoviště                                                                                                                                                                                                                                                      </t>
   </si>
   <si>
-    <t xml:space="preserve">Staphylea pinnata L.                                         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">klokoč zpeřený                               </t>
-  </si>
-  <si>
-    <t xml:space="preserve">KLZ          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">plody-výroba korálků, květy jedlé,                                                                                             </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tradiční okrasný keř vesnických intravilánů pro širokou škálu stanovišt                                                                                                                                                                                                                                            </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frangula alnus Mill.                                         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">krušina olšová                               </t>
-  </si>
-  <si>
-    <t xml:space="preserve">KRO          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">střelný prach                                                                                   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">medonosné, kůra v lékařství                                                                                                    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">doplňková dřevina pro vlhké lokality od nížin do hor                                                                                                                                                                                                                                                               </t>
-  </si>
-  <si>
     <t xml:space="preserve">Rubus idaeus L. aj.                                          </t>
   </si>
   <si>
@@ -1863,37 +1715,13 @@
     <t xml:space="preserve">Doplňková produkční, funkční a estetická dřevina (keř). Vhodná pro ochrané živé ploty, opláštění (trnité)                                                                                                                                                                                                          </t>
   </si>
   <si>
-    <t xml:space="preserve">Ribes uva-crispa L.                                          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">srstka angrešt - meruzalka srstka duplikace  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRA          </t>
-  </si>
-  <si>
     <t xml:space="preserve">(0)-(1)   </t>
   </si>
   <si>
     <t xml:space="preserve">Produkční ovocný keř na bohatá a slunná stanoviště                                                                                                                                                                                                                                                                 </t>
   </si>
   <si>
-    <t xml:space="preserve">Cornus sanguinea  L.                                         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">svída krvavá                                 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SVK          </t>
-  </si>
-  <si>
     <t xml:space="preserve">řezbářství, násady, hůlky                                                                       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">krmné plody                                                                                                                    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">funkční a estetická dřevina (malý stom, keř), množení i řízky                                                                                                                                                                                                                                                      </t>
   </si>
   <si>
     <t xml:space="preserve">Prunus spinosa L.                                            </t>
@@ -2696,7 +2524,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2722,67 +2550,60 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="justify"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="justify"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="justify"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="justify"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="12" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="12" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2791,29 +2612,6 @@
     <cellStyle name="Správně" xfId="1" builtinId="26"/>
   </cellStyles>
   <dxfs count="33">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="238"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -2873,6 +2671,29 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -2969,8 +2790,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{39D85702-16DB-4377-A93A-D2A2B5CDFD41}" name="dataCzech" displayName="dataCzech" ref="A1:AM96" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:AM96" xr:uid="{39D85702-16DB-4377-A93A-D2A2B5CDFD41}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{39D85702-16DB-4377-A93A-D2A2B5CDFD41}" name="dataCzech" displayName="dataCzech" ref="A1:AM85" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:AM85" xr:uid="{39D85702-16DB-4377-A93A-D2A2B5CDFD41}"/>
   <tableColumns count="39">
     <tableColumn id="1" xr3:uid="{BD0856ED-A478-4A2D-B9EE-9ADC3B1F710C}" uniqueName="1" name="Latin_name                                                  " queryTableFieldId="1" dataDxfId="32"/>
     <tableColumn id="2" xr3:uid="{FEDEDE74-B281-488D-AFAA-46DCAA3C5416}" uniqueName="2" name="Scientific_name                                   " queryTableFieldId="2" dataDxfId="31"/>
@@ -2982,35 +2803,35 @@
     <tableColumn id="8" xr3:uid="{9C28FC01-0BBB-4697-A40B-C6D3E23502E6}" uniqueName="8" name="approval " queryTableFieldId="8" dataDxfId="25"/>
     <tableColumn id="9" xr3:uid="{BD3F83FD-890C-4245-803B-3CCA3BC072E6}" uniqueName="9" name="endengeredG " queryTableFieldId="9" dataDxfId="24"/>
     <tableColumn id="10" xr3:uid="{C08C7E67-FB04-48DE-957B-77A2B2CD7A1F}" uniqueName="10" name="endengeredU " queryTableFieldId="10" dataDxfId="23"/>
-    <tableColumn id="11" xr3:uid="{AE72AC59-39B7-4D04-AC0F-E7154B076668}" uniqueName="11" name="endengeredY " queryTableFieldId="11" dataDxfId="2"/>
-    <tableColumn id="12" xr3:uid="{41BE79C0-ED5E-488C-B695-BAD121758619}" uniqueName="12" name="height    " queryTableFieldId="12" dataDxfId="0"/>
-    <tableColumn id="13" xr3:uid="{FA854BD2-6D22-4DEA-A11D-822F0995399B}" uniqueName="13" name="habitus             " queryTableFieldId="13" dataDxfId="1"/>
-    <tableColumn id="14" xr3:uid="{6A4C824D-8B53-458B-962A-02DCE691485A}" uniqueName="14" name="growthspeed     " queryTableFieldId="14" dataDxfId="22"/>
-    <tableColumn id="15" xr3:uid="{3EE3B1B0-5321-411D-AA1B-5753D0312385}" uniqueName="15" name="coppice       " queryTableFieldId="15" dataDxfId="21"/>
+    <tableColumn id="11" xr3:uid="{AE72AC59-39B7-4D04-AC0F-E7154B076668}" uniqueName="11" name="endengeredY " queryTableFieldId="11" dataDxfId="22"/>
+    <tableColumn id="12" xr3:uid="{41BE79C0-ED5E-488C-B695-BAD121758619}" uniqueName="12" name="height    " queryTableFieldId="12" dataDxfId="21"/>
+    <tableColumn id="13" xr3:uid="{FA854BD2-6D22-4DEA-A11D-822F0995399B}" uniqueName="13" name="habitus             " queryTableFieldId="13" dataDxfId="20"/>
+    <tableColumn id="14" xr3:uid="{6A4C824D-8B53-458B-962A-02DCE691485A}" uniqueName="14" name="growthspeed     " queryTableFieldId="14" dataDxfId="19"/>
+    <tableColumn id="15" xr3:uid="{3EE3B1B0-5321-411D-AA1B-5753D0312385}" uniqueName="15" name="coppice       " queryTableFieldId="15" dataDxfId="18"/>
     <tableColumn id="16" xr3:uid="{33D1D1DF-3B50-44EB-9031-B0BCB6B28965}" uniqueName="16" name="Subsidy_anex2 " queryTableFieldId="16"/>
     <tableColumn id="17" xr3:uid="{697939B1-075E-47B6-9CAA-57746BE0417D}" uniqueName="17" name="Subsidy_anex1 " queryTableFieldId="17"/>
     <tableColumn id="18" xr3:uid="{B99B984C-41C8-46F9-AB9C-F3722522FF3B}" uniqueName="18" name="No_subsidy " queryTableFieldId="18"/>
-    <tableColumn id="19" xr3:uid="{567A44D3-E7E2-4C4A-91FE-F29F04102F66}" uniqueName="19" name="Earliness of leaf emergence III-V (flowering date) " queryTableFieldId="19" dataDxfId="20"/>
-    <tableColumn id="20" xr3:uid="{0CA35D18-6C9D-4A66-A0FB-9B2355E5CA0B}" uniqueName="20" name="climateclass " queryTableFieldId="20" dataDxfId="19"/>
-    <tableColumn id="21" xr3:uid="{EDBB1062-AE65-4553-8BA7-66C095158307}" uniqueName="21" name="altitude     " queryTableFieldId="21" dataDxfId="18"/>
-    <tableColumn id="22" xr3:uid="{6B19A82A-FA1D-4537-B080-B866550435A9}" uniqueName="22" name="soil_fertility_acidic " queryTableFieldId="22" dataDxfId="17"/>
-    <tableColumn id="23" xr3:uid="{34211A8E-A22A-4079-ACA1-2CA48B9EC0F1}" uniqueName="23" name="soil_fertility_normal " queryTableFieldId="23" dataDxfId="16"/>
-    <tableColumn id="24" xr3:uid="{09D2F751-52E0-4F4F-90F3-E5C0595A6EEC}" uniqueName="24" name="soil_fertility_rich " queryTableFieldId="24" dataDxfId="15"/>
-    <tableColumn id="25" xr3:uid="{C802CFEF-0709-4D51-A0D3-52C1FA40D07B}" uniqueName="25" name="soil_fertility_nitrogen " queryTableFieldId="25" dataDxfId="14"/>
+    <tableColumn id="19" xr3:uid="{567A44D3-E7E2-4C4A-91FE-F29F04102F66}" uniqueName="19" name="Earliness of leaf emergence III-V (flowering date) " queryTableFieldId="19" dataDxfId="17"/>
+    <tableColumn id="20" xr3:uid="{0CA35D18-6C9D-4A66-A0FB-9B2355E5CA0B}" uniqueName="20" name="climateclass " queryTableFieldId="20" dataDxfId="16"/>
+    <tableColumn id="21" xr3:uid="{EDBB1062-AE65-4553-8BA7-66C095158307}" uniqueName="21" name="altitude     " queryTableFieldId="21" dataDxfId="15"/>
+    <tableColumn id="22" xr3:uid="{6B19A82A-FA1D-4537-B080-B866550435A9}" uniqueName="22" name="soil_fertility_acidic " queryTableFieldId="22" dataDxfId="14"/>
+    <tableColumn id="23" xr3:uid="{34211A8E-A22A-4079-ACA1-2CA48B9EC0F1}" uniqueName="23" name="soil_fertility_normal " queryTableFieldId="23" dataDxfId="13"/>
+    <tableColumn id="24" xr3:uid="{09D2F751-52E0-4F4F-90F3-E5C0595A6EEC}" uniqueName="24" name="soil_fertility_rich " queryTableFieldId="24" dataDxfId="12"/>
+    <tableColumn id="25" xr3:uid="{C802CFEF-0709-4D51-A0D3-52C1FA40D07B}" uniqueName="25" name="soil_fertility_nitrogen " queryTableFieldId="25" dataDxfId="11"/>
     <tableColumn id="26" xr3:uid="{594CC075-4180-45B2-A29E-A72DACA3FEBF}" uniqueName="26" name="soil_fertility_calcium " queryTableFieldId="26"/>
     <tableColumn id="27" xr3:uid="{2507A3FF-5849-4DB8-BBD5-DDF8E1904165}" uniqueName="27" name="soil_fertility_peat " queryTableFieldId="27"/>
-    <tableColumn id="28" xr3:uid="{2ED1CA5A-B3CC-437D-8F58-B6D131941479}" uniqueName="28" name="soil_water_waterlogged " queryTableFieldId="28" dataDxfId="13"/>
-    <tableColumn id="29" xr3:uid="{A2D88D6F-CD78-4828-8477-87BDC87D24E6}" uniqueName="29" name="soil_water_normal " queryTableFieldId="29" dataDxfId="12"/>
-    <tableColumn id="30" xr3:uid="{7B785927-133B-4D03-85C9-B8218EE27759}" uniqueName="30" name="soil_water_arid " queryTableFieldId="30" dataDxfId="11"/>
-    <tableColumn id="31" xr3:uid="{30F8F9CF-1774-47AF-A8F8-2C1796AAA9D0}" uniqueName="31" name="light_demanding " queryTableFieldId="31" dataDxfId="10"/>
-    <tableColumn id="32" xr3:uid="{E1C7BC50-9E7E-4F57-BC39-30C5B3B13D0F}" uniqueName="32" name="light_normal " queryTableFieldId="32" dataDxfId="9"/>
+    <tableColumn id="28" xr3:uid="{2ED1CA5A-B3CC-437D-8F58-B6D131941479}" uniqueName="28" name="soil_water_waterlogged " queryTableFieldId="28" dataDxfId="10"/>
+    <tableColumn id="29" xr3:uid="{A2D88D6F-CD78-4828-8477-87BDC87D24E6}" uniqueName="29" name="soil_water_normal " queryTableFieldId="29" dataDxfId="9"/>
+    <tableColumn id="30" xr3:uid="{7B785927-133B-4D03-85C9-B8218EE27759}" uniqueName="30" name="soil_water_arid " queryTableFieldId="30" dataDxfId="8"/>
+    <tableColumn id="31" xr3:uid="{30F8F9CF-1774-47AF-A8F8-2C1796AAA9D0}" uniqueName="31" name="light_demanding " queryTableFieldId="31" dataDxfId="7"/>
+    <tableColumn id="32" xr3:uid="{E1C7BC50-9E7E-4F57-BC39-30C5B3B13D0F}" uniqueName="32" name="light_normal " queryTableFieldId="32" dataDxfId="6"/>
     <tableColumn id="33" xr3:uid="{D99F5F73-6B21-405B-8410-7EACE29432E2}" uniqueName="33" name="light_undemanding " queryTableFieldId="33"/>
-    <tableColumn id="34" xr3:uid="{525C4C7F-30B7-457B-89BC-2F6322EBE4FA}" uniqueName="34" name="wood                                                                                            " queryTableFieldId="34" dataDxfId="8"/>
-    <tableColumn id="35" xr3:uid="{598836D6-AD45-4F25-A16D-32A7CC7B8810}" uniqueName="35" name="food                                                                                                                           " queryTableFieldId="35" dataDxfId="7"/>
-    <tableColumn id="36" xr3:uid="{E5A8928C-9F32-4BC1-8D37-8B7D4AC53C93}" uniqueName="36" name="Usage                                                                                                                                                                                                                                                          " queryTableFieldId="36" dataDxfId="6"/>
-    <tableColumn id="37" xr3:uid="{3E624905-A6F1-4D50-BCC6-2A6186A75A24}" uniqueName="37" name="floweringdate " queryTableFieldId="37" dataDxfId="5"/>
-    <tableColumn id="38" xr3:uid="{7A852EF5-D459-4B82-AAF7-28D3238F7A75}" uniqueName="38" name="earlinessleafing " queryTableFieldId="38" dataDxfId="4"/>
-    <tableColumn id="39" xr3:uid="{C1403BC7-C1D8-4750-A2F0-04FF74A0816B}" uniqueName="39" name="Undergrowth" queryTableFieldId="39" dataDxfId="3"/>
+    <tableColumn id="34" xr3:uid="{525C4C7F-30B7-457B-89BC-2F6322EBE4FA}" uniqueName="34" name="wood                                                                                            " queryTableFieldId="34" dataDxfId="5"/>
+    <tableColumn id="35" xr3:uid="{598836D6-AD45-4F25-A16D-32A7CC7B8810}" uniqueName="35" name="food                                                                                                                           " queryTableFieldId="35" dataDxfId="4"/>
+    <tableColumn id="36" xr3:uid="{E5A8928C-9F32-4BC1-8D37-8B7D4AC53C93}" uniqueName="36" name="Usage                                                                                                                                                                                                                                                          " queryTableFieldId="36" dataDxfId="3"/>
+    <tableColumn id="37" xr3:uid="{3E624905-A6F1-4D50-BCC6-2A6186A75A24}" uniqueName="37" name="floweringdate " queryTableFieldId="37" dataDxfId="2"/>
+    <tableColumn id="38" xr3:uid="{7A852EF5-D459-4B82-AAF7-28D3238F7A75}" uniqueName="38" name="earlinessleafing " queryTableFieldId="38" dataDxfId="1"/>
+    <tableColumn id="39" xr3:uid="{C1403BC7-C1D8-4750-A2F0-04FF74A0816B}" uniqueName="39" name="Undergrowth" queryTableFieldId="39" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3333,49 +3154,49 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE97AE85-90C5-442A-B63E-0CFF82265B42}">
-  <dimension ref="A1:AM111"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AM100"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="58" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.1328125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.3984375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.1328125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="16" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" style="32" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="48.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.86328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.73046875" style="24" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.1328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.3984375" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="17.1328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.1328125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="48.73046875" style="8" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="15" style="8" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.3984375" style="8" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="21" style="8" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="22" style="8" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="19" style="8" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="23.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="25.140625" style="7" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="20.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="17.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="18.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="81.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="23.265625" style="8" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="22.73046875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="19.73046875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="25.1328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="20.265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17.265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="18.73046875" style="7" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.86328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="21.1328125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="81.1328125" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="96" customWidth="1"/>
-    <col min="36" max="36" width="81.140625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="81.1328125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="16.265625" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="18.265625" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3409,7 +3230,7 @@
       <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="32" t="s">
+      <c r="L1" s="24" t="s">
         <v>11</v>
       </c>
       <c r="M1" t="s">
@@ -3482,7 +3303,7 @@
         <v>34</v>
       </c>
       <c r="AJ1" t="s">
-        <v>666</v>
+        <v>609</v>
       </c>
       <c r="AK1" t="s">
         <v>35</v>
@@ -3494,7 +3315,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -3528,7 +3349,7 @@
       <c r="K2" t="s">
         <v>46</v>
       </c>
-      <c r="L2" s="32" t="s">
+      <c r="L2" s="24" t="s">
         <v>47</v>
       </c>
       <c r="M2" t="s">
@@ -3607,7 +3428,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>60</v>
       </c>
@@ -3641,7 +3462,7 @@
       <c r="K3" t="s">
         <v>46</v>
       </c>
-      <c r="L3" s="32" t="s">
+      <c r="L3" s="24" t="s">
         <v>64</v>
       </c>
       <c r="M3" t="s">
@@ -3720,7 +3541,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>75</v>
       </c>
@@ -3754,7 +3575,7 @@
       <c r="K4" t="s">
         <v>46</v>
       </c>
-      <c r="L4" s="32" t="s">
+      <c r="L4" s="24" t="s">
         <v>78</v>
       </c>
       <c r="M4" t="s">
@@ -3830,7 +3651,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>89</v>
       </c>
@@ -3864,7 +3685,7 @@
       <c r="K5" t="s">
         <v>46</v>
       </c>
-      <c r="L5" s="32" t="s">
+      <c r="L5" s="24" t="s">
         <v>92</v>
       </c>
       <c r="M5" t="s">
@@ -3943,7 +3764,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>101</v>
       </c>
@@ -3977,7 +3798,7 @@
       <c r="K6" t="s">
         <v>46</v>
       </c>
-      <c r="L6" s="32" t="s">
+      <c r="L6" s="24" t="s">
         <v>106</v>
       </c>
       <c r="M6" t="s">
@@ -4053,7 +3874,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>114</v>
       </c>
@@ -4087,7 +3908,7 @@
       <c r="K7" t="s">
         <v>46</v>
       </c>
-      <c r="L7" s="32" t="s">
+      <c r="L7" s="24" t="s">
         <v>106</v>
       </c>
       <c r="M7" t="s">
@@ -4163,7 +3984,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>120</v>
       </c>
@@ -4197,7 +4018,7 @@
       <c r="K8" t="s">
         <v>46</v>
       </c>
-      <c r="L8" s="32" t="s">
+      <c r="L8" s="24" t="s">
         <v>123</v>
       </c>
       <c r="M8" t="s">
@@ -4276,7 +4097,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>131</v>
       </c>
@@ -4310,7 +4131,7 @@
       <c r="K9" t="s">
         <v>46</v>
       </c>
-      <c r="L9" s="32" t="s">
+      <c r="L9" s="24" t="s">
         <v>92</v>
       </c>
       <c r="M9" t="s">
@@ -4386,7 +4207,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>138</v>
       </c>
@@ -4420,7 +4241,7 @@
       <c r="K10" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="32" t="s">
+      <c r="L10" s="24" t="s">
         <v>78</v>
       </c>
       <c r="M10" t="s">
@@ -4496,7 +4317,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>144</v>
       </c>
@@ -4530,7 +4351,7 @@
       <c r="K11" t="s">
         <v>105</v>
       </c>
-      <c r="L11" s="32" t="s">
+      <c r="L11" s="24" t="s">
         <v>147</v>
       </c>
       <c r="M11" t="s">
@@ -4609,7 +4430,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>149</v>
       </c>
@@ -4643,7 +4464,7 @@
       <c r="K12" t="s">
         <v>46</v>
       </c>
-      <c r="L12" s="32" t="s">
+      <c r="L12" s="24" t="s">
         <v>78</v>
       </c>
       <c r="M12" t="s">
@@ -4719,7 +4540,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>155</v>
       </c>
@@ -4753,7 +4574,7 @@
       <c r="K13" t="s">
         <v>46</v>
       </c>
-      <c r="L13" s="32" t="s">
+      <c r="L13" s="24" t="s">
         <v>106</v>
       </c>
       <c r="M13" t="s">
@@ -4832,7 +4653,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>160</v>
       </c>
@@ -4866,7 +4687,7 @@
       <c r="K14" t="s">
         <v>46</v>
       </c>
-      <c r="L14" s="32" t="s">
+      <c r="L14" s="24" t="s">
         <v>163</v>
       </c>
       <c r="M14" t="s">
@@ -4942,7 +4763,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>167</v>
       </c>
@@ -4976,7 +4797,7 @@
       <c r="K15" t="s">
         <v>46</v>
       </c>
-      <c r="L15" s="32" t="s">
+      <c r="L15" s="24" t="s">
         <v>163</v>
       </c>
       <c r="M15" t="s">
@@ -5052,7 +4873,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>173</v>
       </c>
@@ -5086,7 +4907,7 @@
       <c r="K16" t="s">
         <v>46</v>
       </c>
-      <c r="L16" s="32" t="s">
+      <c r="L16" s="24" t="s">
         <v>176</v>
       </c>
       <c r="M16" t="s">
@@ -5162,7 +4983,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="17" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>178</v>
       </c>
@@ -5196,7 +5017,7 @@
       <c r="K17" t="s">
         <v>46</v>
       </c>
-      <c r="L17" s="32" t="s">
+      <c r="L17" s="24" t="s">
         <v>181</v>
       </c>
       <c r="M17" t="s">
@@ -5272,7 +5093,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>185</v>
       </c>
@@ -5306,7 +5127,7 @@
       <c r="K18" t="s">
         <v>46</v>
       </c>
-      <c r="L18" s="32" t="s">
+      <c r="L18" s="24" t="s">
         <v>188</v>
       </c>
       <c r="M18" t="s">
@@ -5382,7 +5203,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>192</v>
       </c>
@@ -5416,7 +5237,7 @@
       <c r="K19" t="s">
         <v>46</v>
       </c>
-      <c r="L19" s="32" t="s">
+      <c r="L19" s="24" t="s">
         <v>195</v>
       </c>
       <c r="M19" t="s">
@@ -5492,7 +5313,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>198</v>
       </c>
@@ -5526,7 +5347,7 @@
       <c r="K20" t="s">
         <v>46</v>
       </c>
-      <c r="L20" s="32" t="s">
+      <c r="L20" s="24" t="s">
         <v>201</v>
       </c>
       <c r="M20" t="s">
@@ -5605,7 +5426,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>206</v>
       </c>
@@ -5639,7 +5460,7 @@
       <c r="K21" t="s">
         <v>46</v>
       </c>
-      <c r="L21" s="32" t="s">
+      <c r="L21" s="24" t="s">
         <v>210</v>
       </c>
       <c r="M21" t="s">
@@ -5718,7 +5539,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="22" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>212</v>
       </c>
@@ -5752,7 +5573,7 @@
       <c r="K22" t="s">
         <v>46</v>
       </c>
-      <c r="L22" s="32" t="s">
+      <c r="L22" s="24" t="s">
         <v>201</v>
       </c>
       <c r="M22" t="s">
@@ -5831,7 +5652,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>218</v>
       </c>
@@ -5865,7 +5686,7 @@
       <c r="K23" t="s">
         <v>46</v>
       </c>
-      <c r="L23" s="32" t="s">
+      <c r="L23" s="24" t="s">
         <v>221</v>
       </c>
       <c r="M23" t="s">
@@ -5944,7 +5765,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>226</v>
       </c>
@@ -5978,7 +5799,7 @@
       <c r="K24" t="s">
         <v>46</v>
       </c>
-      <c r="L24" s="32" t="s">
+      <c r="L24" s="24" t="s">
         <v>92</v>
       </c>
       <c r="M24" t="s">
@@ -6057,7 +5878,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="25" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>233</v>
       </c>
@@ -6091,7 +5912,7 @@
       <c r="K25" t="s">
         <v>46</v>
       </c>
-      <c r="L25" s="32" t="s">
+      <c r="L25" s="24" t="s">
         <v>106</v>
       </c>
       <c r="M25" t="s">
@@ -6170,7 +5991,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="26" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>240</v>
       </c>
@@ -6204,7 +6025,7 @@
       <c r="K26" t="s">
         <v>46</v>
       </c>
-      <c r="L26" s="32" t="s">
+      <c r="L26" s="24" t="s">
         <v>163</v>
       </c>
       <c r="M26" t="s">
@@ -6283,7 +6104,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>247</v>
       </c>
@@ -6317,7 +6138,7 @@
       <c r="K27" t="s">
         <v>46</v>
       </c>
-      <c r="L27" s="32" t="s">
+      <c r="L27" s="24" t="s">
         <v>250</v>
       </c>
       <c r="M27" t="s">
@@ -6396,7 +6217,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="28" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>253</v>
       </c>
@@ -6430,7 +6251,7 @@
       <c r="K28" t="s">
         <v>46</v>
       </c>
-      <c r="L28" s="32" t="s">
+      <c r="L28" s="24" t="s">
         <v>221</v>
       </c>
       <c r="M28" t="s">
@@ -6509,7 +6330,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="29" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>258</v>
       </c>
@@ -6543,7 +6364,7 @@
       <c r="K29" t="s">
         <v>46</v>
       </c>
-      <c r="L29" s="32" t="s">
+      <c r="L29" s="24" t="s">
         <v>250</v>
       </c>
       <c r="M29" t="s">
@@ -6619,7 +6440,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>263</v>
       </c>
@@ -6653,7 +6474,7 @@
       <c r="K30" t="s">
         <v>46</v>
       </c>
-      <c r="L30" s="32" t="s">
+      <c r="L30" s="24" t="s">
         <v>221</v>
       </c>
       <c r="M30" t="s">
@@ -6732,7 +6553,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>271</v>
       </c>
@@ -6766,7 +6587,7 @@
       <c r="K31" t="s">
         <v>46</v>
       </c>
-      <c r="L31" s="32" t="s">
+      <c r="L31" s="24" t="s">
         <v>221</v>
       </c>
       <c r="M31" t="s">
@@ -6845,7 +6666,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="32" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>275</v>
       </c>
@@ -6879,7 +6700,7 @@
       <c r="K32" t="s">
         <v>46</v>
       </c>
-      <c r="L32" s="32" t="s">
+      <c r="L32" s="24" t="s">
         <v>163</v>
       </c>
       <c r="M32" t="s">
@@ -6955,7 +6776,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="33" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>282</v>
       </c>
@@ -6989,7 +6810,7 @@
       <c r="K33" t="s">
         <v>46</v>
       </c>
-      <c r="L33" s="32" t="s">
+      <c r="L33" s="24" t="s">
         <v>78</v>
       </c>
       <c r="M33" t="s">
@@ -7068,7 +6889,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="34" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>290</v>
       </c>
@@ -7102,7 +6923,7 @@
       <c r="K34" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="32" t="s">
+      <c r="L34" s="24" t="s">
         <v>106</v>
       </c>
       <c r="M34" t="s">
@@ -7178,7 +6999,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>298</v>
       </c>
@@ -7212,7 +7033,7 @@
       <c r="K35" t="s">
         <v>46</v>
       </c>
-      <c r="L35" s="32" t="s">
+      <c r="L35" s="24" t="s">
         <v>92</v>
       </c>
       <c r="M35" t="s">
@@ -7291,7 +7112,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="36" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>302</v>
       </c>
@@ -7325,7 +7146,7 @@
       <c r="K36" t="s">
         <v>46</v>
       </c>
-      <c r="L36" s="32" t="s">
+      <c r="L36" s="24" t="s">
         <v>163</v>
       </c>
       <c r="M36" t="s">
@@ -7404,7 +7225,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>309</v>
       </c>
@@ -7438,7 +7259,7 @@
       <c r="K37" t="s">
         <v>46</v>
       </c>
-      <c r="L37" s="32" t="s">
+      <c r="L37" s="24" t="s">
         <v>195</v>
       </c>
       <c r="M37" t="s">
@@ -7517,7 +7338,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>314</v>
       </c>
@@ -7551,7 +7372,7 @@
       <c r="K38" t="s">
         <v>46</v>
       </c>
-      <c r="L38" s="32" t="s">
+      <c r="L38" s="24" t="s">
         <v>317</v>
       </c>
       <c r="M38" t="s">
@@ -7630,7 +7451,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="39" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>320</v>
       </c>
@@ -7664,7 +7485,7 @@
       <c r="K39" t="s">
         <v>46</v>
       </c>
-      <c r="L39" s="32" t="s">
+      <c r="L39" s="24" t="s">
         <v>323</v>
       </c>
       <c r="M39" t="s">
@@ -7743,7 +7564,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="40" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>328</v>
       </c>
@@ -7777,7 +7598,7 @@
       <c r="K40" t="s">
         <v>46</v>
       </c>
-      <c r="L40" s="32" t="s">
+      <c r="L40" s="24" t="s">
         <v>331</v>
       </c>
       <c r="M40" t="s">
@@ -7853,7 +7674,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="41" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>335</v>
       </c>
@@ -7887,7 +7708,7 @@
       <c r="K41" t="s">
         <v>46</v>
       </c>
-      <c r="L41" s="32" t="s">
+      <c r="L41" s="24" t="s">
         <v>338</v>
       </c>
       <c r="M41" t="s">
@@ -7963,7 +7784,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="42" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>341</v>
       </c>
@@ -7997,7 +7818,7 @@
       <c r="K42" t="s">
         <v>46</v>
       </c>
-      <c r="L42" s="32" t="s">
+      <c r="L42" s="24" t="s">
         <v>344</v>
       </c>
       <c r="M42" t="s">
@@ -8073,7 +7894,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="43" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>348</v>
       </c>
@@ -8107,7 +7928,7 @@
       <c r="K43" t="s">
         <v>46</v>
       </c>
-      <c r="L43" s="32" t="s">
+      <c r="L43" s="24" t="s">
         <v>106</v>
       </c>
       <c r="M43" t="s">
@@ -8183,7 +8004,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="44" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>356</v>
       </c>
@@ -8217,7 +8038,7 @@
       <c r="K44" t="s">
         <v>46</v>
       </c>
-      <c r="L44" s="32" t="s">
+      <c r="L44" s="24" t="s">
         <v>359</v>
       </c>
       <c r="M44" t="s">
@@ -8296,7 +8117,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="45" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>362</v>
       </c>
@@ -8330,7 +8151,7 @@
       <c r="K45" t="s">
         <v>46</v>
       </c>
-      <c r="L45" s="32" t="s">
+      <c r="L45" s="24" t="s">
         <v>47</v>
       </c>
       <c r="M45" t="s">
@@ -8406,7 +8227,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>367</v>
       </c>
@@ -8440,7 +8261,7 @@
       <c r="K46" t="s">
         <v>46</v>
       </c>
-      <c r="L46" s="32" t="s">
+      <c r="L46" s="24" t="s">
         <v>317</v>
       </c>
       <c r="M46" t="s">
@@ -8516,7 +8337,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="47" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>373</v>
       </c>
@@ -8550,7 +8371,7 @@
       <c r="K47" t="s">
         <v>46</v>
       </c>
-      <c r="L47" s="32" t="s">
+      <c r="L47" s="24" t="s">
         <v>376</v>
       </c>
       <c r="M47" t="s">
@@ -8626,7 +8447,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="48" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>379</v>
       </c>
@@ -8660,7 +8481,7 @@
       <c r="K48" t="s">
         <v>46</v>
       </c>
-      <c r="L48" s="32" t="s">
+      <c r="L48" s="24" t="s">
         <v>382</v>
       </c>
       <c r="M48" t="s">
@@ -8736,7 +8557,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>386</v>
       </c>
@@ -8770,7 +8591,7 @@
       <c r="K49" t="s">
         <v>46</v>
       </c>
-      <c r="L49" s="32" t="s">
+      <c r="L49" s="24" t="s">
         <v>92</v>
       </c>
       <c r="M49" t="s">
@@ -8846,7 +8667,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="50" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>392</v>
       </c>
@@ -8880,7 +8701,7 @@
       <c r="K50" t="s">
         <v>46</v>
       </c>
-      <c r="L50" s="32" t="s">
+      <c r="L50" s="24" t="s">
         <v>92</v>
       </c>
       <c r="M50" t="s">
@@ -8956,7 +8777,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="51" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>398</v>
       </c>
@@ -8990,7 +8811,7 @@
       <c r="K51" t="s">
         <v>46</v>
       </c>
-      <c r="L51" s="32" t="s">
+      <c r="L51" s="24" t="s">
         <v>401</v>
       </c>
       <c r="M51" t="s">
@@ -9066,7 +8887,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="52" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>404</v>
       </c>
@@ -9100,7 +8921,7 @@
       <c r="K52" t="s">
         <v>46</v>
       </c>
-      <c r="L52" s="32" t="s">
+      <c r="L52" s="24" t="s">
         <v>407</v>
       </c>
       <c r="M52" t="s">
@@ -9176,7 +8997,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="53" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>411</v>
       </c>
@@ -9210,7 +9031,7 @@
       <c r="K53" t="s">
         <v>46</v>
       </c>
-      <c r="L53" s="32" t="s">
+      <c r="L53" s="24" t="s">
         <v>414</v>
       </c>
       <c r="M53" t="s">
@@ -9289,7 +9110,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="54" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>417</v>
       </c>
@@ -9323,7 +9144,7 @@
       <c r="K54" t="s">
         <v>46</v>
       </c>
-      <c r="L54" s="32" t="s">
+      <c r="L54" s="24" t="s">
         <v>420</v>
       </c>
       <c r="M54" t="s">
@@ -9399,7 +9220,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="55" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>424</v>
       </c>
@@ -9433,7 +9254,7 @@
       <c r="K55" t="s">
         <v>46</v>
       </c>
-      <c r="L55" s="32" t="s">
+      <c r="L55" s="24" t="s">
         <v>427</v>
       </c>
       <c r="M55" t="s">
@@ -9509,7 +9330,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="56" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>431</v>
       </c>
@@ -9543,7 +9364,7 @@
       <c r="K56" t="s">
         <v>46</v>
       </c>
-      <c r="L56" s="32" t="s">
+      <c r="L56" s="24" t="s">
         <v>106</v>
       </c>
       <c r="M56" t="s">
@@ -9619,7 +9440,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="57" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>437</v>
       </c>
@@ -9653,7 +9474,7 @@
       <c r="K57" t="s">
         <v>46</v>
       </c>
-      <c r="L57" s="32" t="s">
+      <c r="L57" s="24" t="s">
         <v>440</v>
       </c>
       <c r="M57" t="s">
@@ -9729,7 +9550,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="58" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>444</v>
       </c>
@@ -9763,7 +9584,7 @@
       <c r="K58" t="s">
         <v>46</v>
       </c>
-      <c r="L58" s="32" t="s">
+      <c r="L58" s="24" t="s">
         <v>176</v>
       </c>
       <c r="M58" t="s">
@@ -9839,7 +9660,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="59" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>450</v>
       </c>
@@ -9873,7 +9694,7 @@
       <c r="K59" t="s">
         <v>46</v>
       </c>
-      <c r="L59" s="32" t="s">
+      <c r="L59" s="24" t="s">
         <v>453</v>
       </c>
       <c r="M59" t="s">
@@ -9949,7 +9770,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="60" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>455</v>
       </c>
@@ -9983,7 +9804,7 @@
       <c r="K60" t="s">
         <v>46</v>
       </c>
-      <c r="L60" s="32" t="s">
+      <c r="L60" s="24" t="s">
         <v>317</v>
       </c>
       <c r="M60" t="s">
@@ -10059,7 +9880,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>460</v>
       </c>
@@ -10093,7 +9914,7 @@
       <c r="K61" t="s">
         <v>46</v>
       </c>
-      <c r="L61" s="32" t="s">
+      <c r="L61" s="24" t="s">
         <v>463</v>
       </c>
       <c r="M61" t="s">
@@ -10169,15 +9990,15 @@
         <v>59</v>
       </c>
     </row>
-    <row r="62" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B62" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="C62" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="D62" t="s">
         <v>63</v>
@@ -10195,61 +10016,61 @@
         <v>45</v>
       </c>
       <c r="I62" t="s">
-        <v>105</v>
+        <v>46</v>
       </c>
       <c r="J62" t="s">
-        <v>105</v>
+        <v>46</v>
       </c>
       <c r="K62" t="s">
-        <v>105</v>
-      </c>
-      <c r="L62" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="L62" s="24" t="s">
+        <v>476</v>
+      </c>
+      <c r="M62" t="s">
         <v>472</v>
-      </c>
-      <c r="M62" t="s">
-        <v>464</v>
       </c>
       <c r="N62" t="s">
         <v>66</v>
       </c>
       <c r="O62" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="P62">
         <v>0</v>
       </c>
       <c r="Q62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S62" s="8" t="s">
         <v>465</v>
       </c>
       <c r="T62" s="8" t="s">
-        <v>243</v>
+        <v>52</v>
       </c>
       <c r="U62" s="8" t="s">
-        <v>110</v>
+        <v>278</v>
       </c>
       <c r="V62" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W62" s="8">
         <v>2</v>
       </c>
       <c r="X62" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB62" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC62" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD62" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE62" s="7">
         <v>3</v>
@@ -10261,16 +10082,16 @@
         <v>1</v>
       </c>
       <c r="AH62" t="s">
-        <v>473</v>
+        <v>70</v>
       </c>
       <c r="AI62" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="AJ62" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AK62" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="AL62" t="s">
         <v>355</v>
@@ -10279,24 +10100,24 @@
         <v>100</v>
       </c>
     </row>
-    <row r="63" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B63" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C63" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="D63" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="E63" t="s">
         <v>42</v>
       </c>
       <c r="F63" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G63" t="s">
         <v>44</v>
@@ -10313,50 +10134,50 @@
       <c r="K63" t="s">
         <v>46</v>
       </c>
-      <c r="L63" s="32" t="s">
-        <v>64</v>
+      <c r="L63" s="24" t="s">
+        <v>78</v>
       </c>
       <c r="M63" t="s">
-        <v>464</v>
+        <v>79</v>
       </c>
       <c r="N63" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="O63" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="P63">
         <v>0</v>
       </c>
       <c r="Q63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S63" s="8" t="s">
         <v>465</v>
       </c>
       <c r="T63" s="8" t="s">
-        <v>223</v>
+        <v>482</v>
       </c>
       <c r="U63" s="8" t="s">
-        <v>110</v>
+        <v>83</v>
       </c>
       <c r="V63" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W63" s="8">
         <v>2</v>
       </c>
       <c r="X63" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB63" s="7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC63" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD63" s="7">
         <v>1</v>
@@ -10368,39 +10189,39 @@
         <v>2</v>
       </c>
       <c r="AG63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH63" t="s">
-        <v>70</v>
+        <v>483</v>
       </c>
       <c r="AI63" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="AJ63" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="AK63" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="AL63" t="s">
         <v>355</v>
       </c>
       <c r="AM63" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
     </row>
-    <row r="64" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="B64" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="C64" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
       <c r="D64" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="E64" t="s">
         <v>42</v>
@@ -10415,16 +10236,16 @@
         <v>45</v>
       </c>
       <c r="I64" t="s">
-        <v>46</v>
+        <v>105</v>
       </c>
       <c r="J64" t="s">
-        <v>46</v>
+        <v>105</v>
       </c>
       <c r="K64" t="s">
         <v>46</v>
       </c>
-      <c r="L64" s="32" t="s">
-        <v>484</v>
+      <c r="L64" s="24" t="s">
+        <v>489</v>
       </c>
       <c r="M64" t="s">
         <v>464</v>
@@ -10433,25 +10254,25 @@
         <v>66</v>
       </c>
       <c r="O64" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="P64">
         <v>0</v>
       </c>
       <c r="Q64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S64" s="8" t="s">
         <v>465</v>
       </c>
       <c r="T64" s="8" t="s">
-        <v>68</v>
+        <v>223</v>
       </c>
       <c r="U64" s="8" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="V64" s="8">
         <v>0</v>
@@ -10460,7 +10281,7 @@
         <v>2</v>
       </c>
       <c r="X64" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB64" s="7">
         <v>0</v>
@@ -10469,10 +10290,10 @@
         <v>2</v>
       </c>
       <c r="AD64" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE64" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF64" s="7">
         <v>2</v>
@@ -10481,16 +10302,16 @@
         <v>0</v>
       </c>
       <c r="AH64" t="s">
-        <v>70</v>
+        <v>469</v>
       </c>
       <c r="AI64" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="AJ64" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="AK64" t="s">
-        <v>57</v>
+        <v>217</v>
       </c>
       <c r="AL64" t="s">
         <v>355</v>
@@ -10499,18 +10320,18 @@
         <v>100</v>
       </c>
     </row>
-    <row r="65" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="B65" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C65" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="D65" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="E65" t="s">
         <v>42</v>
@@ -10533,11 +10354,11 @@
       <c r="K65" t="s">
         <v>46</v>
       </c>
-      <c r="L65" s="32" t="s">
-        <v>490</v>
+      <c r="L65" s="24" t="s">
+        <v>470</v>
       </c>
       <c r="M65" t="s">
-        <v>491</v>
+        <v>464</v>
       </c>
       <c r="N65" t="s">
         <v>66</v>
@@ -10549,58 +10370,58 @@
         <v>0</v>
       </c>
       <c r="Q65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S65" s="8" t="s">
         <v>465</v>
       </c>
       <c r="T65" s="8" t="s">
-        <v>153</v>
+        <v>223</v>
       </c>
       <c r="U65" s="8" t="s">
-        <v>135</v>
+        <v>158</v>
       </c>
       <c r="V65" s="8">
         <v>0</v>
       </c>
       <c r="W65" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X65" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB65" s="7">
         <v>0</v>
       </c>
       <c r="AC65" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD65" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE65" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF65" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG65">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH65" t="s">
-        <v>70</v>
+        <v>469</v>
       </c>
       <c r="AI65" t="s">
-        <v>422</v>
+        <v>495</v>
       </c>
       <c r="AJ65" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="AK65" t="s">
-        <v>113</v>
+        <v>57</v>
       </c>
       <c r="AL65" t="s">
         <v>355</v>
@@ -10609,15 +10430,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="66" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="B66" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C66" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="D66" t="s">
         <v>63</v>
@@ -10643,8 +10464,8 @@
       <c r="K66" t="s">
         <v>46</v>
       </c>
-      <c r="L66" s="32" t="s">
-        <v>496</v>
+      <c r="L66" s="24" t="s">
+        <v>323</v>
       </c>
       <c r="M66" t="s">
         <v>464</v>
@@ -10659,19 +10480,19 @@
         <v>0</v>
       </c>
       <c r="Q66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S66" s="8" t="s">
         <v>465</v>
       </c>
       <c r="T66" s="8" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="U66" s="8" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="V66" s="8">
         <v>0</v>
@@ -10680,16 +10501,16 @@
         <v>2</v>
       </c>
       <c r="X66" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB66" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC66" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD66" s="7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE66" s="7">
         <v>3</v>
@@ -10698,19 +10519,19 @@
         <v>2</v>
       </c>
       <c r="AG66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH66" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AI66" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AJ66" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AK66" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="AL66" t="s">
         <v>355</v>
@@ -10719,15 +10540,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="67" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B67" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C67" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D67" t="s">
         <v>63</v>
@@ -10753,17 +10574,17 @@
       <c r="K67" t="s">
         <v>46</v>
       </c>
-      <c r="L67" s="32" t="s">
-        <v>503</v>
+      <c r="L67" s="24" t="s">
+        <v>505</v>
       </c>
       <c r="M67" t="s">
-        <v>491</v>
+        <v>464</v>
       </c>
       <c r="N67" t="s">
         <v>66</v>
       </c>
       <c r="O67" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="P67">
         <v>0</v>
@@ -10778,28 +10599,28 @@
         <v>465</v>
       </c>
       <c r="T67" s="8" t="s">
-        <v>52</v>
+        <v>236</v>
       </c>
       <c r="U67" s="8" t="s">
-        <v>278</v>
+        <v>506</v>
       </c>
       <c r="V67" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W67" s="8">
         <v>2</v>
       </c>
       <c r="X67" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB67" s="7">
         <v>2</v>
       </c>
       <c r="AC67" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD67" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE67" s="7">
         <v>3</v>
@@ -10808,19 +10629,19 @@
         <v>2</v>
       </c>
       <c r="AG67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH67" t="s">
-        <v>70</v>
+        <v>499</v>
       </c>
       <c r="AI67" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="AJ67" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="AK67" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="AL67" t="s">
         <v>355</v>
@@ -10829,27 +10650,27 @@
         <v>100</v>
       </c>
     </row>
-    <row r="68" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B68" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C68" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="D68" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="E68" t="s">
+        <v>43</v>
+      </c>
+      <c r="F68" t="s">
         <v>42</v>
       </c>
-      <c r="F68" t="s">
-        <v>43</v>
-      </c>
       <c r="G68" t="s">
-        <v>44</v>
+        <v>104</v>
       </c>
       <c r="H68" t="s">
         <v>45</v>
@@ -10863,11 +10684,11 @@
       <c r="K68" t="s">
         <v>46</v>
       </c>
-      <c r="L68" s="32" t="s">
-        <v>78</v>
+      <c r="L68" s="24" t="s">
+        <v>147</v>
       </c>
       <c r="M68" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="N68" t="s">
         <v>93</v>
@@ -10888,49 +10709,49 @@
         <v>465</v>
       </c>
       <c r="T68" s="8" t="s">
-        <v>509</v>
+        <v>68</v>
       </c>
       <c r="U68" s="8" t="s">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="V68" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W68" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X68" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB68" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC68" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD68" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE68" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AF68" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG68">
         <v>0</v>
       </c>
       <c r="AH68" t="s">
-        <v>510</v>
+        <v>70</v>
       </c>
       <c r="AI68" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AJ68" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AK68" t="s">
-        <v>119</v>
+        <v>57</v>
       </c>
       <c r="AL68" t="s">
         <v>355</v>
@@ -10939,15 +10760,15 @@
         <v>59</v>
       </c>
     </row>
-    <row r="69" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B69" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C69" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D69" t="s">
         <v>63</v>
@@ -10973,17 +10794,17 @@
       <c r="K69" t="s">
         <v>46</v>
       </c>
-      <c r="L69" s="32" t="s">
-        <v>420</v>
+      <c r="L69" s="24" t="s">
+        <v>517</v>
       </c>
       <c r="M69" t="s">
-        <v>491</v>
+        <v>464</v>
       </c>
       <c r="N69" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="O69" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="P69">
         <v>0</v>
@@ -10998,7 +10819,7 @@
         <v>465</v>
       </c>
       <c r="T69" s="8" t="s">
-        <v>223</v>
+        <v>68</v>
       </c>
       <c r="U69" s="8" t="s">
         <v>110</v>
@@ -11012,9 +10833,6 @@
       <c r="X69" s="8">
         <v>3</v>
       </c>
-      <c r="Z69">
-        <v>2</v>
-      </c>
       <c r="AB69" s="7">
         <v>0</v>
       </c>
@@ -11034,16 +10852,16 @@
         <v>0</v>
       </c>
       <c r="AH69" t="s">
-        <v>516</v>
+        <v>70</v>
       </c>
       <c r="AI69" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AJ69" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AK69" t="s">
-        <v>57</v>
+        <v>113</v>
       </c>
       <c r="AL69" t="s">
         <v>355</v>
@@ -11052,18 +10870,18 @@
         <v>100</v>
       </c>
     </row>
-    <row r="70" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B70" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C70" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D70" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="E70" t="s">
         <v>42</v>
@@ -11078,22 +10896,22 @@
         <v>45</v>
       </c>
       <c r="I70" t="s">
-        <v>105</v>
+        <v>46</v>
       </c>
       <c r="J70" t="s">
-        <v>105</v>
+        <v>46</v>
       </c>
       <c r="K70" t="s">
         <v>46</v>
       </c>
-      <c r="L70" s="32" t="s">
-        <v>522</v>
+      <c r="L70" s="24" t="s">
+        <v>476</v>
       </c>
       <c r="M70" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="N70" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="O70" t="s">
         <v>107</v>
@@ -11111,13 +10929,13 @@
         <v>465</v>
       </c>
       <c r="T70" s="8" t="s">
-        <v>223</v>
+        <v>466</v>
       </c>
       <c r="U70" s="8" t="s">
-        <v>135</v>
+        <v>53</v>
       </c>
       <c r="V70" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W70" s="8">
         <v>2</v>
@@ -11126,34 +10944,34 @@
         <v>2</v>
       </c>
       <c r="AB70" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC70" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD70" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE70" s="7">
         <v>2</v>
       </c>
       <c r="AF70" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH70" t="s">
-        <v>473</v>
+        <v>70</v>
       </c>
       <c r="AI70" t="s">
+        <v>422</v>
+      </c>
+      <c r="AJ70" t="s">
         <v>523</v>
       </c>
-      <c r="AJ70" t="s">
-        <v>524</v>
-      </c>
       <c r="AK70" t="s">
-        <v>217</v>
+        <v>57</v>
       </c>
       <c r="AL70" t="s">
         <v>355</v>
@@ -11162,18 +10980,18 @@
         <v>100</v>
       </c>
     </row>
-    <row r="71" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
+        <v>524</v>
+      </c>
+      <c r="B71" t="s">
         <v>525</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
         <v>526</v>
       </c>
-      <c r="C71" t="s">
-        <v>527</v>
-      </c>
       <c r="D71" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="E71" t="s">
         <v>42</v>
@@ -11185,7 +11003,7 @@
         <v>44</v>
       </c>
       <c r="H71" t="s">
-        <v>45</v>
+        <v>209</v>
       </c>
       <c r="I71" t="s">
         <v>46</v>
@@ -11196,11 +11014,11 @@
       <c r="K71" t="s">
         <v>46</v>
       </c>
-      <c r="L71" s="32" t="s">
-        <v>484</v>
+      <c r="L71" s="24" t="s">
+        <v>527</v>
       </c>
       <c r="M71" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="N71" t="s">
         <v>66</v>
@@ -11221,19 +11039,19 @@
         <v>465</v>
       </c>
       <c r="T71" s="8" t="s">
-        <v>223</v>
+        <v>345</v>
       </c>
       <c r="U71" s="8" t="s">
-        <v>158</v>
+        <v>268</v>
       </c>
       <c r="V71" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W71" s="8">
         <v>2</v>
       </c>
       <c r="X71" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB71" s="7">
         <v>0</v>
@@ -11242,28 +11060,28 @@
         <v>2</v>
       </c>
       <c r="AD71" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE71" s="7">
         <v>2</v>
       </c>
       <c r="AF71" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG71">
         <v>0</v>
       </c>
       <c r="AH71" t="s">
-        <v>473</v>
+        <v>70</v>
       </c>
       <c r="AI71" t="s">
         <v>528</v>
       </c>
       <c r="AJ71" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="AK71" t="s">
-        <v>57</v>
+        <v>217</v>
       </c>
       <c r="AL71" t="s">
         <v>355</v>
@@ -11272,27 +11090,27 @@
         <v>100</v>
       </c>
     </row>
-    <row r="72" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B72" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C72" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D72" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="E72" t="s">
         <v>42</v>
       </c>
       <c r="F72" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G72" t="s">
-        <v>44</v>
+        <v>104</v>
       </c>
       <c r="H72" t="s">
         <v>45</v>
@@ -11306,17 +11124,17 @@
       <c r="K72" t="s">
         <v>46</v>
       </c>
-      <c r="L72" s="32" t="s">
-        <v>323</v>
+      <c r="L72" s="24" t="s">
+        <v>453</v>
       </c>
       <c r="M72" t="s">
-        <v>464</v>
+        <v>65</v>
       </c>
       <c r="N72" t="s">
         <v>93</v>
       </c>
       <c r="O72" t="s">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="P72">
         <v>0</v>
@@ -11331,66 +11149,66 @@
         <v>465</v>
       </c>
       <c r="T72" s="8" t="s">
-        <v>153</v>
+        <v>533</v>
       </c>
       <c r="U72" s="8" t="s">
-        <v>135</v>
+        <v>534</v>
       </c>
       <c r="V72" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W72" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X72" s="8">
         <v>2</v>
       </c>
       <c r="AB72" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC72" s="7">
         <v>2</v>
       </c>
       <c r="AD72" s="7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE72" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF72" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH72" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="AI72" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="AJ72" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="AK72" t="s">
-        <v>143</v>
+        <v>73</v>
       </c>
       <c r="AL72" t="s">
         <v>355</v>
       </c>
       <c r="AM72" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
     </row>
-    <row r="73" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="B73" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C73" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="D73" t="s">
         <v>63</v>
@@ -11405,7 +11223,7 @@
         <v>44</v>
       </c>
       <c r="H73" t="s">
-        <v>45</v>
+        <v>209</v>
       </c>
       <c r="I73" t="s">
         <v>46</v>
@@ -11416,17 +11234,17 @@
       <c r="K73" t="s">
         <v>46</v>
       </c>
-      <c r="L73" s="32" t="s">
-        <v>538</v>
+      <c r="L73" s="24" t="s">
+        <v>541</v>
       </c>
       <c r="M73" t="s">
         <v>464</v>
       </c>
       <c r="N73" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="O73" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="P73">
         <v>0</v>
@@ -11441,10 +11259,10 @@
         <v>465</v>
       </c>
       <c r="T73" s="8" t="s">
-        <v>236</v>
+        <v>153</v>
       </c>
       <c r="U73" s="8" t="s">
-        <v>539</v>
+        <v>53</v>
       </c>
       <c r="V73" s="8">
         <v>2</v>
@@ -11453,10 +11271,10 @@
         <v>2</v>
       </c>
       <c r="X73" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB73" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC73" s="7">
         <v>2</v>
@@ -11474,16 +11292,16 @@
         <v>0</v>
       </c>
       <c r="AH73" t="s">
-        <v>532</v>
+        <v>70</v>
       </c>
       <c r="AI73" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="AJ73" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AK73" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="AL73" t="s">
         <v>355</v>
@@ -11492,27 +11310,27 @@
         <v>100</v>
       </c>
     </row>
-    <row r="74" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B74" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C74" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D74" t="s">
         <v>63</v>
       </c>
       <c r="E74" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F74" t="s">
         <v>42</v>
       </c>
       <c r="G74" t="s">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="H74" t="s">
         <v>45</v>
@@ -11526,17 +11344,17 @@
       <c r="K74" t="s">
         <v>46</v>
       </c>
-      <c r="L74" s="32" t="s">
-        <v>147</v>
+      <c r="L74" s="24" t="s">
+        <v>471</v>
       </c>
       <c r="M74" t="s">
-        <v>65</v>
+        <v>472</v>
       </c>
       <c r="N74" t="s">
         <v>93</v>
       </c>
       <c r="O74" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="P74">
         <v>0</v>
@@ -11551,34 +11369,34 @@
         <v>465</v>
       </c>
       <c r="T74" s="8" t="s">
-        <v>68</v>
+        <v>345</v>
       </c>
       <c r="U74" s="8" t="s">
-        <v>158</v>
+        <v>547</v>
       </c>
       <c r="V74" s="8">
         <v>0</v>
       </c>
       <c r="W74" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X74" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB74" s="7">
         <v>0</v>
       </c>
       <c r="AC74" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD74" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE74" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF74" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AG74">
         <v>0</v>
@@ -11587,36 +11405,36 @@
         <v>70</v>
       </c>
       <c r="AI74" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="AJ74" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="AK74" t="s">
-        <v>57</v>
+        <v>129</v>
       </c>
       <c r="AL74" t="s">
         <v>355</v>
       </c>
       <c r="AM74" t="s">
-        <v>59</v>
+        <v>100</v>
       </c>
     </row>
-    <row r="75" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="B75" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="C75" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="D75" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="E75" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F75" t="s">
         <v>42</v>
@@ -11636,11 +11454,11 @@
       <c r="K75" t="s">
         <v>46</v>
       </c>
-      <c r="L75" s="32" t="s">
+      <c r="L75" s="24" t="s">
         <v>463</v>
       </c>
       <c r="M75" t="s">
-        <v>491</v>
+        <v>472</v>
       </c>
       <c r="N75" t="s">
         <v>93</v>
@@ -11661,13 +11479,13 @@
         <v>465</v>
       </c>
       <c r="T75" s="8" t="s">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="U75" s="8" t="s">
-        <v>268</v>
+        <v>135</v>
       </c>
       <c r="V75" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W75" s="8">
         <v>2</v>
@@ -11676,7 +11494,7 @@
         <v>2</v>
       </c>
       <c r="AB75" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC75" s="7">
         <v>3</v>
@@ -11688,22 +11506,22 @@
         <v>2</v>
       </c>
       <c r="AF75" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG75">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH75" t="s">
         <v>70</v>
       </c>
       <c r="AI75" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="AJ75" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="AK75" t="s">
-        <v>129</v>
+        <v>57</v>
       </c>
       <c r="AL75" t="s">
         <v>355</v>
@@ -11712,15 +11530,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="76" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="B76" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="C76" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="D76" t="s">
         <v>63</v>
@@ -11746,8 +11564,8 @@
       <c r="K76" t="s">
         <v>46</v>
       </c>
-      <c r="L76" s="32" t="s">
-        <v>555</v>
+      <c r="L76" s="24" t="s">
+        <v>561</v>
       </c>
       <c r="M76" t="s">
         <v>464</v>
@@ -11756,7 +11574,7 @@
         <v>66</v>
       </c>
       <c r="O76" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="P76">
         <v>0</v>
@@ -11771,10 +11589,10 @@
         <v>465</v>
       </c>
       <c r="T76" s="8" t="s">
-        <v>68</v>
+        <v>153</v>
       </c>
       <c r="U76" s="8" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="V76" s="8">
         <v>0</v>
@@ -11783,7 +11601,10 @@
         <v>2</v>
       </c>
       <c r="X76" s="8">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="Z76">
+        <v>2</v>
       </c>
       <c r="AB76" s="7">
         <v>0</v>
@@ -11795,7 +11616,7 @@
         <v>3</v>
       </c>
       <c r="AE76" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF76" s="7">
         <v>2</v>
@@ -11804,13 +11625,13 @@
         <v>0</v>
       </c>
       <c r="AH76" t="s">
-        <v>70</v>
+        <v>557</v>
       </c>
       <c r="AI76" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="AJ76" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="AK76" t="s">
         <v>113</v>
@@ -11822,21 +11643,21 @@
         <v>100</v>
       </c>
     </row>
-    <row r="77" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="B77" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="C77" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="D77" t="s">
         <v>41</v>
       </c>
       <c r="E77" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F77" t="s">
         <v>42</v>
@@ -11856,14 +11677,14 @@
       <c r="K77" t="s">
         <v>46</v>
       </c>
-      <c r="L77" s="32" t="s">
-        <v>463</v>
+      <c r="L77" s="24" t="s">
+        <v>489</v>
       </c>
       <c r="M77" t="s">
-        <v>491</v>
+        <v>464</v>
       </c>
       <c r="N77" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="O77" t="s">
         <v>107</v>
@@ -11881,10 +11702,10 @@
         <v>465</v>
       </c>
       <c r="T77" s="8" t="s">
-        <v>286</v>
+        <v>223</v>
       </c>
       <c r="U77" s="8" t="s">
-        <v>110</v>
+        <v>278</v>
       </c>
       <c r="V77" s="8">
         <v>0</v>
@@ -11893,63 +11714,63 @@
         <v>2</v>
       </c>
       <c r="X77" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB77" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC77" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD77" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE77" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF77" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH77" t="s">
-        <v>70</v>
+        <v>567</v>
       </c>
       <c r="AI77" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="AJ77" t="s">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="AK77" t="s">
-        <v>57</v>
+        <v>119</v>
       </c>
       <c r="AL77" t="s">
         <v>355</v>
       </c>
       <c r="AM77" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
     </row>
-    <row r="78" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
-        <v>563</v>
+        <v>570</v>
       </c>
       <c r="B78" t="s">
-        <v>564</v>
+        <v>571</v>
       </c>
       <c r="C78" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="D78" t="s">
         <v>41</v>
       </c>
       <c r="E78" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F78" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G78" t="s">
         <v>44</v>
@@ -11958,22 +11779,22 @@
         <v>45</v>
       </c>
       <c r="I78" t="s">
-        <v>105</v>
+        <v>46</v>
       </c>
       <c r="J78" t="s">
-        <v>105</v>
+        <v>46</v>
       </c>
       <c r="K78" t="s">
         <v>46</v>
       </c>
-      <c r="L78" s="32" t="s">
-        <v>472</v>
+      <c r="L78" s="24" t="s">
+        <v>573</v>
       </c>
       <c r="M78" t="s">
-        <v>464</v>
+        <v>124</v>
       </c>
       <c r="N78" t="s">
-        <v>93</v>
+        <v>49</v>
       </c>
       <c r="O78" t="s">
         <v>107</v>
@@ -11991,78 +11812,75 @@
         <v>465</v>
       </c>
       <c r="T78" s="8" t="s">
-        <v>153</v>
+        <v>82</v>
       </c>
       <c r="U78" s="8" t="s">
-        <v>268</v>
+        <v>83</v>
       </c>
       <c r="V78" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W78" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X78" s="8">
-        <v>1</v>
-      </c>
-      <c r="AA78">
         <v>2</v>
       </c>
       <c r="AB78" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC78" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD78" s="7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE78" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF78" s="7">
         <v>2</v>
       </c>
       <c r="AG78">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH78" t="s">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="AI78" t="s">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c r="AJ78" t="s">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="AK78" t="s">
-        <v>57</v>
+        <v>119</v>
       </c>
       <c r="AL78" t="s">
         <v>355</v>
       </c>
       <c r="AM78" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
     </row>
-    <row r="79" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="B79" t="s">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="C79" t="s">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="D79" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="E79" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F79" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G79" t="s">
         <v>44</v>
@@ -12079,11 +11897,11 @@
       <c r="K79" t="s">
         <v>46</v>
       </c>
-      <c r="L79" s="32" t="s">
-        <v>503</v>
+      <c r="L79" s="24" t="s">
+        <v>580</v>
       </c>
       <c r="M79" t="s">
-        <v>491</v>
+        <v>464</v>
       </c>
       <c r="N79" t="s">
         <v>49</v>
@@ -12104,69 +11922,69 @@
         <v>465</v>
       </c>
       <c r="T79" s="8" t="s">
-        <v>466</v>
+        <v>581</v>
       </c>
       <c r="U79" s="8" t="s">
-        <v>53</v>
+        <v>278</v>
       </c>
       <c r="V79" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W79" s="8">
         <v>2</v>
       </c>
       <c r="X79" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB79" s="7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC79" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD79" s="7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE79" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF79" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG79">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH79" t="s">
-        <v>70</v>
+        <v>582</v>
       </c>
       <c r="AI79" t="s">
-        <v>422</v>
+        <v>583</v>
       </c>
       <c r="AJ79" t="s">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="AK79" t="s">
-        <v>57</v>
+        <v>119</v>
       </c>
       <c r="AL79" t="s">
         <v>355</v>
       </c>
       <c r="AM79" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
     </row>
-    <row r="80" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
-        <v>573</v>
+        <v>585</v>
       </c>
       <c r="B80" t="s">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="C80" t="s">
-        <v>575</v>
+        <v>452</v>
       </c>
       <c r="D80" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="E80" t="s">
         <v>42</v>
@@ -12175,28 +11993,28 @@
         <v>42</v>
       </c>
       <c r="G80" t="s">
-        <v>44</v>
+        <v>104</v>
       </c>
       <c r="H80" t="s">
-        <v>209</v>
+        <v>45</v>
       </c>
       <c r="I80" t="s">
-        <v>46</v>
+        <v>105</v>
       </c>
       <c r="J80" t="s">
-        <v>46</v>
+        <v>105</v>
       </c>
       <c r="K80" t="s">
         <v>46</v>
       </c>
-      <c r="L80" s="32" t="s">
-        <v>576</v>
+      <c r="L80" s="24" t="s">
+        <v>489</v>
       </c>
       <c r="M80" t="s">
-        <v>491</v>
+        <v>464</v>
       </c>
       <c r="N80" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="O80" t="s">
         <v>107</v>
@@ -12214,10 +12032,10 @@
         <v>465</v>
       </c>
       <c r="T80" s="8" t="s">
-        <v>345</v>
+        <v>52</v>
       </c>
       <c r="U80" s="8" t="s">
-        <v>268</v>
+        <v>83</v>
       </c>
       <c r="V80" s="8">
         <v>2</v>
@@ -12226,10 +12044,10 @@
         <v>2</v>
       </c>
       <c r="X80" s="8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB80" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC80" s="7">
         <v>2</v>
@@ -12238,42 +12056,42 @@
         <v>1</v>
       </c>
       <c r="AE80" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF80" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG80">
         <v>0</v>
       </c>
       <c r="AH80" t="s">
-        <v>70</v>
+        <v>567</v>
       </c>
       <c r="AI80" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="AJ80" t="s">
-        <v>578</v>
+        <v>587</v>
       </c>
       <c r="AK80" t="s">
-        <v>217</v>
+        <v>119</v>
       </c>
       <c r="AL80" t="s">
         <v>355</v>
       </c>
       <c r="AM80" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
     </row>
-    <row r="81" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
-        <v>579</v>
+        <v>588</v>
       </c>
       <c r="B81" t="s">
-        <v>580</v>
+        <v>589</v>
       </c>
       <c r="C81" t="s">
-        <v>581</v>
+        <v>590</v>
       </c>
       <c r="D81" t="s">
         <v>41</v>
@@ -12282,10 +12100,10 @@
         <v>42</v>
       </c>
       <c r="F81" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G81" t="s">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="H81" t="s">
         <v>45</v>
@@ -12299,17 +12117,17 @@
       <c r="K81" t="s">
         <v>46</v>
       </c>
-      <c r="L81" s="32" t="s">
-        <v>453</v>
+      <c r="L81" s="24" t="s">
+        <v>541</v>
       </c>
       <c r="M81" t="s">
-        <v>65</v>
+        <v>464</v>
       </c>
       <c r="N81" t="s">
-        <v>93</v>
+        <v>49</v>
       </c>
       <c r="O81" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="P81">
         <v>0</v>
@@ -12324,19 +12142,19 @@
         <v>465</v>
       </c>
       <c r="T81" s="8" t="s">
-        <v>582</v>
+        <v>236</v>
       </c>
       <c r="U81" s="8" t="s">
-        <v>583</v>
+        <v>591</v>
       </c>
       <c r="V81" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W81" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X81" s="8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB81" s="7">
         <v>3</v>
@@ -12348,25 +12166,25 @@
         <v>0</v>
       </c>
       <c r="AE81" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF81" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH81" t="s">
-        <v>584</v>
+        <v>70</v>
       </c>
       <c r="AI81" t="s">
-        <v>585</v>
+        <v>448</v>
       </c>
       <c r="AJ81" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="AK81" t="s">
-        <v>73</v>
+        <v>129</v>
       </c>
       <c r="AL81" t="s">
         <v>355</v>
@@ -12375,18 +12193,18 @@
         <v>59</v>
       </c>
     </row>
-    <row r="82" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="B82" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="C82" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D82" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="E82" t="s">
         <v>42</v>
@@ -12395,31 +12213,31 @@
         <v>42</v>
       </c>
       <c r="G82" t="s">
-        <v>44</v>
+        <v>104</v>
       </c>
       <c r="H82" t="s">
-        <v>209</v>
+        <v>45</v>
       </c>
       <c r="I82" t="s">
-        <v>46</v>
+        <v>105</v>
       </c>
       <c r="J82" t="s">
-        <v>46</v>
+        <v>105</v>
       </c>
       <c r="K82" t="s">
         <v>46</v>
       </c>
-      <c r="L82" s="32" t="s">
-        <v>590</v>
+      <c r="L82" s="24" t="s">
+        <v>595</v>
       </c>
       <c r="M82" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="N82" t="s">
         <v>93</v>
       </c>
       <c r="O82" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="P82">
         <v>0</v>
@@ -12434,7 +12252,7 @@
         <v>465</v>
       </c>
       <c r="T82" s="8" t="s">
-        <v>153</v>
+        <v>82</v>
       </c>
       <c r="U82" s="8" t="s">
         <v>53</v>
@@ -12446,16 +12264,16 @@
         <v>2</v>
       </c>
       <c r="X82" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB82" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC82" s="7">
         <v>2</v>
       </c>
       <c r="AD82" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE82" s="7">
         <v>3</v>
@@ -12470,10 +12288,10 @@
         <v>70</v>
       </c>
       <c r="AI82" t="s">
-        <v>591</v>
+        <v>448</v>
       </c>
       <c r="AJ82" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="AK82" t="s">
         <v>119</v>
@@ -12482,21 +12300,21 @@
         <v>355</v>
       </c>
       <c r="AM82" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
     </row>
-    <row r="83" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="B83" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="C83" t="s">
-        <v>595</v>
+        <v>457</v>
       </c>
       <c r="D83" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="E83" t="s">
         <v>42</v>
@@ -12505,7 +12323,7 @@
         <v>42</v>
       </c>
       <c r="G83" t="s">
-        <v>44</v>
+        <v>104</v>
       </c>
       <c r="H83" t="s">
         <v>45</v>
@@ -12519,11 +12337,11 @@
       <c r="K83" t="s">
         <v>46</v>
       </c>
-      <c r="L83" s="32" t="s">
-        <v>490</v>
+      <c r="L83" s="24" t="s">
+        <v>210</v>
       </c>
       <c r="M83" t="s">
-        <v>491</v>
+        <v>464</v>
       </c>
       <c r="N83" t="s">
         <v>93</v>
@@ -12544,34 +12362,34 @@
         <v>465</v>
       </c>
       <c r="T83" s="8" t="s">
-        <v>345</v>
+        <v>581</v>
       </c>
       <c r="U83" s="8" t="s">
-        <v>596</v>
+        <v>278</v>
       </c>
       <c r="V83" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W83" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X83" s="8">
         <v>2</v>
       </c>
       <c r="AB83" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC83" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD83" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE83" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF83" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG83">
         <v>0</v>
@@ -12580,36 +12398,36 @@
         <v>70</v>
       </c>
       <c r="AI83" t="s">
-        <v>597</v>
+        <v>568</v>
       </c>
       <c r="AJ83" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AK83" t="s">
-        <v>129</v>
+        <v>217</v>
       </c>
       <c r="AL83" t="s">
         <v>355</v>
       </c>
       <c r="AM83" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
     </row>
-    <row r="84" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B84" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C84" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D84" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="E84" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F84" t="s">
         <v>42</v>
@@ -12621,19 +12439,19 @@
         <v>45</v>
       </c>
       <c r="I84" t="s">
-        <v>46</v>
+        <v>105</v>
       </c>
       <c r="J84" t="s">
-        <v>46</v>
+        <v>105</v>
       </c>
       <c r="K84" t="s">
         <v>46</v>
       </c>
-      <c r="L84" s="32" t="s">
-        <v>463</v>
+      <c r="L84" s="24" t="s">
+        <v>470</v>
       </c>
       <c r="M84" t="s">
-        <v>491</v>
+        <v>472</v>
       </c>
       <c r="N84" t="s">
         <v>93</v>
@@ -12654,10 +12472,10 @@
         <v>465</v>
       </c>
       <c r="T84" s="8" t="s">
-        <v>164</v>
+        <v>223</v>
       </c>
       <c r="U84" s="8" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="V84" s="8">
         <v>0</v>
@@ -12666,19 +12484,19 @@
         <v>2</v>
       </c>
       <c r="X84" s="8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AB84" s="7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC84" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD84" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE84" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF84" s="7">
         <v>2</v>
@@ -12687,33 +12505,33 @@
         <v>0</v>
       </c>
       <c r="AH84" t="s">
-        <v>70</v>
+        <v>567</v>
       </c>
       <c r="AI84" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="AJ84" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AK84" t="s">
-        <v>57</v>
+        <v>119</v>
       </c>
       <c r="AL84" t="s">
         <v>355</v>
       </c>
       <c r="AM84" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
     </row>
-    <row r="85" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:39" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B85" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C85" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D85" t="s">
         <v>63</v>
@@ -12739,11 +12557,11 @@
       <c r="K85" t="s">
         <v>46</v>
       </c>
-      <c r="L85" s="32" t="s">
-        <v>607</v>
+      <c r="L85" s="24" t="s">
+        <v>471</v>
       </c>
       <c r="M85" t="s">
-        <v>491</v>
+        <v>472</v>
       </c>
       <c r="N85" t="s">
         <v>66</v>
@@ -12764,19 +12582,19 @@
         <v>465</v>
       </c>
       <c r="T85" s="8" t="s">
-        <v>243</v>
+        <v>95</v>
       </c>
       <c r="U85" s="8" t="s">
-        <v>278</v>
+        <v>53</v>
       </c>
       <c r="V85" s="8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W85" s="8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X85" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB85" s="7">
         <v>1</v>
@@ -12794,39 +12612,39 @@
         <v>2</v>
       </c>
       <c r="AG85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH85" t="s">
         <v>70</v>
       </c>
       <c r="AI85" t="s">
-        <v>422</v>
+        <v>608</v>
       </c>
       <c r="AJ85" t="s">
-        <v>608</v>
+        <v>556</v>
       </c>
       <c r="AK85" t="s">
-        <v>113</v>
+        <v>57</v>
       </c>
       <c r="AL85" t="s">
         <v>355</v>
       </c>
       <c r="AM85" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
     </row>
-    <row r="86" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>609</v>
-      </c>
-      <c r="B86" t="s">
+    <row r="86" spans="1:39" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A86" s="9" t="s">
+        <v>677</v>
+      </c>
+      <c r="B86" s="10" t="s">
         <v>610</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C86" s="11" t="s">
         <v>611</v>
       </c>
       <c r="D86" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="E86" t="s">
         <v>42</v>
@@ -12835,31 +12653,31 @@
         <v>42</v>
       </c>
       <c r="G86" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="H86" t="s">
         <v>45</v>
       </c>
       <c r="I86" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J86" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K86" t="s">
-        <v>46</v>
-      </c>
-      <c r="L86" s="32" t="s">
-        <v>472</v>
+        <v>45</v>
+      </c>
+      <c r="L86" s="12" t="s">
+        <v>691</v>
       </c>
       <c r="M86" t="s">
-        <v>491</v>
+        <v>464</v>
       </c>
       <c r="N86" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="O86" t="s">
-        <v>80</v>
+        <v>107</v>
       </c>
       <c r="P86">
         <v>0</v>
@@ -12870,53 +12688,52 @@
       <c r="R86">
         <v>1</v>
       </c>
-      <c r="S86" s="8" t="s">
-        <v>465</v>
-      </c>
-      <c r="T86" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="U86" s="8" t="s">
-        <v>158</v>
+      <c r="S86" s="13">
+        <v>5</v>
+      </c>
+      <c r="T86" s="12" t="s">
+        <v>699</v>
+      </c>
+      <c r="U86" s="13" t="s">
+        <v>707</v>
       </c>
       <c r="V86" s="8">
-        <v>0</v>
-      </c>
-      <c r="W86" s="8">
-        <v>3</v>
-      </c>
-      <c r="X86" s="8">
-        <v>2</v>
-      </c>
-      <c r="AB86" s="7">
-        <v>2</v>
-      </c>
-      <c r="AC86" s="7">
-        <v>3</v>
-      </c>
-      <c r="AD86" s="7">
-        <v>2</v>
-      </c>
-      <c r="AE86" s="7">
-        <v>2</v>
-      </c>
-      <c r="AF86" s="7">
-        <v>3</v>
-      </c>
-      <c r="AG86">
-        <v>2</v>
-      </c>
-      <c r="AH86" t="s">
+        <v>1</v>
+      </c>
+      <c r="W86" s="14">
+        <v>2</v>
+      </c>
+      <c r="X86" s="14">
+        <v>1</v>
+      </c>
+      <c r="Y86" s="14"/>
+      <c r="AB86" s="15">
+        <v>1</v>
+      </c>
+      <c r="AC86" s="15">
+        <v>1</v>
+      </c>
+      <c r="AD86" s="15">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="16">
+        <v>2</v>
+      </c>
+      <c r="AF86" s="16">
+        <v>1</v>
+      </c>
+      <c r="AG86" s="14">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="17"/>
+      <c r="AI86" s="18" t="s">
         <v>612</v>
       </c>
-      <c r="AI86" t="s">
+      <c r="AJ86" s="19" t="s">
         <v>613</v>
       </c>
-      <c r="AJ86" t="s">
-        <v>614</v>
-      </c>
-      <c r="AK86" t="s">
-        <v>57</v>
+      <c r="AK86" s="13">
+        <v>5</v>
       </c>
       <c r="AL86" t="s">
         <v>355</v>
@@ -12925,15 +12742,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="87" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
+    <row r="87" spans="1:39" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A87" s="9" t="s">
+        <v>678</v>
+      </c>
+      <c r="B87" s="10" t="s">
+        <v>614</v>
+      </c>
+      <c r="C87" s="11" t="s">
         <v>615</v>
-      </c>
-      <c r="B87" t="s">
-        <v>616</v>
-      </c>
-      <c r="C87" t="s">
-        <v>617</v>
       </c>
       <c r="D87" t="s">
         <v>63</v>
@@ -12945,28 +12762,28 @@
         <v>42</v>
       </c>
       <c r="G87" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="H87" t="s">
         <v>45</v>
       </c>
       <c r="I87" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J87" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K87" t="s">
-        <v>46</v>
-      </c>
-      <c r="L87" s="32" t="s">
-        <v>618</v>
+        <v>45</v>
+      </c>
+      <c r="L87" s="12" t="s">
+        <v>692</v>
       </c>
       <c r="M87" t="s">
         <v>464</v>
       </c>
       <c r="N87" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="O87" t="s">
         <v>107</v>
@@ -12980,56 +12797,54 @@
       <c r="R87">
         <v>1</v>
       </c>
-      <c r="S87" s="8" t="s">
-        <v>465</v>
-      </c>
-      <c r="T87" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="U87" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="V87" s="8">
-        <v>0</v>
-      </c>
-      <c r="W87" s="8">
-        <v>2</v>
-      </c>
-      <c r="X87" s="8">
-        <v>2</v>
-      </c>
-      <c r="Z87">
-        <v>2</v>
-      </c>
-      <c r="AB87" s="7">
-        <v>0</v>
-      </c>
-      <c r="AC87" s="7">
-        <v>2</v>
-      </c>
-      <c r="AD87" s="7">
-        <v>3</v>
-      </c>
-      <c r="AE87" s="7">
-        <v>2</v>
-      </c>
-      <c r="AF87" s="7">
-        <v>2</v>
-      </c>
-      <c r="AG87">
-        <v>0</v>
-      </c>
-      <c r="AH87" t="s">
-        <v>612</v>
-      </c>
-      <c r="AI87" t="s">
+      <c r="S87" s="20" t="s">
+        <v>616</v>
+      </c>
+      <c r="T87" s="12" t="s">
+        <v>700</v>
+      </c>
+      <c r="U87" s="13" t="s">
+        <v>708</v>
+      </c>
+      <c r="V87" s="21">
+        <v>0</v>
+      </c>
+      <c r="W87" s="21">
+        <v>1</v>
+      </c>
+      <c r="X87" s="21">
+        <v>2</v>
+      </c>
+      <c r="Y87" s="21"/>
+      <c r="AB87" s="15">
+        <v>1</v>
+      </c>
+      <c r="AC87" s="15">
+        <v>2</v>
+      </c>
+      <c r="AD87" s="15">
+        <v>1</v>
+      </c>
+      <c r="AE87" s="22">
+        <v>2</v>
+      </c>
+      <c r="AF87" s="22">
+        <v>1</v>
+      </c>
+      <c r="AG87" s="21">
+        <v>1</v>
+      </c>
+      <c r="AH87" s="17" t="s">
+        <v>617</v>
+      </c>
+      <c r="AI87" s="18" t="s">
+        <v>618</v>
+      </c>
+      <c r="AJ87" s="19" t="s">
         <v>619</v>
       </c>
-      <c r="AJ87" t="s">
-        <v>620</v>
-      </c>
-      <c r="AK87" t="s">
-        <v>113</v>
+      <c r="AK87" s="20" t="s">
+        <v>713</v>
       </c>
       <c r="AL87" t="s">
         <v>355</v>
@@ -13038,18 +12853,18 @@
         <v>100</v>
       </c>
     </row>
-    <row r="88" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
+    <row r="88" spans="1:39" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A88" s="9" t="s">
+        <v>679</v>
+      </c>
+      <c r="B88" s="10" t="s">
+        <v>620</v>
+      </c>
+      <c r="C88" s="11" t="s">
         <v>621</v>
       </c>
-      <c r="B88" t="s">
-        <v>622</v>
-      </c>
-      <c r="C88" t="s">
-        <v>623</v>
-      </c>
       <c r="D88" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="E88" t="s">
         <v>42</v>
@@ -13058,28 +12873,28 @@
         <v>42</v>
       </c>
       <c r="G88" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="H88" t="s">
         <v>45</v>
       </c>
       <c r="I88" t="s">
-        <v>46</v>
+        <v>105</v>
       </c>
       <c r="J88" t="s">
-        <v>46</v>
+        <v>105</v>
       </c>
       <c r="K88" t="s">
-        <v>46</v>
-      </c>
-      <c r="L88" s="32" t="s">
-        <v>522</v>
+        <v>105</v>
+      </c>
+      <c r="L88" s="12" t="s">
+        <v>693</v>
       </c>
       <c r="M88" t="s">
         <v>464</v>
       </c>
       <c r="N88" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="O88" t="s">
         <v>107</v>
@@ -13093,103 +12908,104 @@
       <c r="R88">
         <v>1</v>
       </c>
-      <c r="S88" s="8" t="s">
-        <v>465</v>
-      </c>
-      <c r="T88" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="U88" s="8" t="s">
-        <v>278</v>
+      <c r="S88" s="20" t="s">
+        <v>622</v>
+      </c>
+      <c r="T88" s="12" t="s">
+        <v>701</v>
+      </c>
+      <c r="U88" s="13" t="s">
+        <v>709</v>
       </c>
       <c r="V88" s="8">
-        <v>0</v>
-      </c>
-      <c r="W88" s="8">
-        <v>2</v>
-      </c>
-      <c r="X88" s="8">
-        <v>2</v>
-      </c>
-      <c r="AB88" s="7">
-        <v>3</v>
-      </c>
-      <c r="AC88" s="7">
-        <v>2</v>
-      </c>
-      <c r="AD88" s="7">
-        <v>0</v>
-      </c>
-      <c r="AE88" s="7">
-        <v>3</v>
-      </c>
-      <c r="AF88" s="7">
-        <v>2</v>
-      </c>
-      <c r="AG88">
-        <v>0</v>
-      </c>
-      <c r="AH88" t="s">
+        <v>1</v>
+      </c>
+      <c r="W88" s="13">
+        <v>1</v>
+      </c>
+      <c r="X88" s="13">
+        <v>2</v>
+      </c>
+      <c r="Y88" s="13"/>
+      <c r="AB88" s="23">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="23">
+        <v>1</v>
+      </c>
+      <c r="AD88" s="23">
+        <v>2</v>
+      </c>
+      <c r="AE88" s="24">
+        <v>2</v>
+      </c>
+      <c r="AF88" s="24">
+        <v>1</v>
+      </c>
+      <c r="AG88" s="13">
+        <v>1</v>
+      </c>
+      <c r="AH88" s="17" t="s">
+        <v>623</v>
+      </c>
+      <c r="AI88" s="18" t="s">
         <v>624</v>
       </c>
-      <c r="AI88" t="s">
+      <c r="AJ88" s="19" t="s">
         <v>625</v>
       </c>
-      <c r="AJ88" t="s">
-        <v>626</v>
-      </c>
-      <c r="AK88" t="s">
-        <v>119</v>
+      <c r="AK88" s="20" t="s">
+        <v>714</v>
       </c>
       <c r="AL88" t="s">
         <v>355</v>
       </c>
       <c r="AM88" t="s">
-        <v>59</v>
+        <v>100</v>
       </c>
     </row>
-    <row r="89" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
+    <row r="89" spans="1:39" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A89" s="9" t="s">
+        <v>680</v>
+      </c>
+      <c r="B89" s="10" t="s">
+        <v>626</v>
+      </c>
+      <c r="C89" s="11" t="s">
         <v>627</v>
       </c>
-      <c r="B89" t="s">
-        <v>628</v>
-      </c>
-      <c r="C89" t="s">
-        <v>629</v>
-      </c>
       <c r="D89" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="E89" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F89" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G89" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="H89" t="s">
         <v>45</v>
       </c>
       <c r="I89" t="s">
-        <v>46</v>
+        <v>105</v>
       </c>
       <c r="J89" t="s">
-        <v>46</v>
+        <v>105</v>
       </c>
       <c r="K89" t="s">
-        <v>46</v>
-      </c>
-      <c r="L89" s="32" t="s">
-        <v>630</v>
+        <v>45</v>
+      </c>
+      <c r="L89" s="12" t="s">
+        <v>716</v>
       </c>
       <c r="M89" t="s">
-        <v>124</v>
+        <v>472</v>
       </c>
       <c r="N89" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="O89" t="s">
         <v>107</v>
@@ -13203,103 +13019,107 @@
       <c r="R89">
         <v>1</v>
       </c>
-      <c r="S89" s="8" t="s">
-        <v>465</v>
-      </c>
-      <c r="T89" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="U89" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="V89" s="8">
-        <v>2</v>
-      </c>
-      <c r="W89" s="8">
-        <v>3</v>
-      </c>
-      <c r="X89" s="8">
-        <v>2</v>
-      </c>
-      <c r="AB89" s="7">
-        <v>1</v>
-      </c>
-      <c r="AC89" s="7">
-        <v>3</v>
-      </c>
-      <c r="AD89" s="7">
-        <v>2</v>
-      </c>
-      <c r="AE89" s="7">
-        <v>3</v>
-      </c>
-      <c r="AF89" s="7">
-        <v>2</v>
-      </c>
-      <c r="AG89">
-        <v>0</v>
-      </c>
-      <c r="AH89" t="s">
-        <v>631</v>
-      </c>
-      <c r="AI89" t="s">
-        <v>632</v>
-      </c>
-      <c r="AJ89" t="s">
-        <v>633</v>
-      </c>
-      <c r="AK89" t="s">
-        <v>119</v>
+      <c r="S89" s="13">
+        <v>5</v>
+      </c>
+      <c r="T89" s="12" t="s">
+        <v>700</v>
+      </c>
+      <c r="U89" s="13" t="s">
+        <v>708</v>
+      </c>
+      <c r="V89" s="13">
+        <v>0</v>
+      </c>
+      <c r="W89" s="13">
+        <v>1</v>
+      </c>
+      <c r="X89" s="13">
+        <v>2</v>
+      </c>
+      <c r="Y89" s="13"/>
+      <c r="Z89">
+        <v>2</v>
+      </c>
+      <c r="AB89" s="23">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="23">
+        <v>1</v>
+      </c>
+      <c r="AD89" s="23">
+        <v>2</v>
+      </c>
+      <c r="AE89" s="24">
+        <v>2</v>
+      </c>
+      <c r="AF89" s="24">
+        <v>1</v>
+      </c>
+      <c r="AG89" s="13">
+        <v>0</v>
+      </c>
+      <c r="AH89" s="17" t="s">
+        <v>628</v>
+      </c>
+      <c r="AI89" s="18" t="s">
+        <v>629</v>
+      </c>
+      <c r="AJ89" s="19" t="s">
+        <v>630</v>
+      </c>
+      <c r="AK89" s="13">
+        <v>5</v>
       </c>
       <c r="AL89" t="s">
         <v>355</v>
       </c>
       <c r="AM89" t="s">
-        <v>59</v>
+        <v>100</v>
       </c>
     </row>
-    <row r="90" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>634</v>
-      </c>
-      <c r="B90" t="s">
-        <v>635</v>
-      </c>
-      <c r="C90" t="s">
-        <v>636</v>
+    <row r="90" spans="1:39" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A90" s="11" t="s">
+        <v>631</v>
+      </c>
+      <c r="B90" s="10" t="s">
+        <v>632</v>
+      </c>
+      <c r="C90" s="11" t="s">
+        <v>633</v>
       </c>
       <c r="D90" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="E90" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F90" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G90" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="H90" t="s">
         <v>45</v>
       </c>
       <c r="I90" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J90" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K90" t="s">
-        <v>46</v>
-      </c>
-      <c r="L90" s="32" t="s">
-        <v>637</v>
+        <v>45</v>
+      </c>
+      <c r="L90" s="24" t="s">
+        <v>471</v>
       </c>
       <c r="M90" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="N90" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="O90" t="s">
         <v>107</v>
@@ -13313,100 +13133,97 @@
       <c r="R90">
         <v>1</v>
       </c>
-      <c r="S90" s="8" t="s">
-        <v>465</v>
-      </c>
-      <c r="T90" s="8" t="s">
-        <v>638</v>
-      </c>
-      <c r="U90" s="8" t="s">
-        <v>278</v>
-      </c>
-      <c r="V90" s="8">
-        <v>0</v>
-      </c>
-      <c r="W90" s="8">
-        <v>2</v>
-      </c>
-      <c r="X90" s="8">
-        <v>3</v>
-      </c>
-      <c r="AB90" s="7">
-        <v>3</v>
-      </c>
-      <c r="AC90" s="7">
-        <v>2</v>
-      </c>
-      <c r="AD90" s="7">
-        <v>0</v>
-      </c>
-      <c r="AE90" s="7">
-        <v>3</v>
-      </c>
-      <c r="AF90" s="7">
-        <v>2</v>
-      </c>
-      <c r="AG90">
-        <v>0</v>
-      </c>
-      <c r="AH90" t="s">
-        <v>639</v>
-      </c>
-      <c r="AI90" t="s">
-        <v>640</v>
-      </c>
-      <c r="AJ90" t="s">
-        <v>641</v>
-      </c>
-      <c r="AK90" t="s">
-        <v>119</v>
+      <c r="S90" s="20" t="s">
+        <v>634</v>
+      </c>
+      <c r="T90" s="24" t="s">
+        <v>702</v>
+      </c>
+      <c r="U90" s="13" t="s">
+        <v>710</v>
+      </c>
+      <c r="V90" s="13">
+        <v>1</v>
+      </c>
+      <c r="W90" s="13">
+        <v>1</v>
+      </c>
+      <c r="X90" s="13">
+        <v>1</v>
+      </c>
+      <c r="Y90" s="13"/>
+      <c r="AB90" s="24">
+        <v>0</v>
+      </c>
+      <c r="AC90" s="24">
+        <v>1</v>
+      </c>
+      <c r="AD90" s="24">
+        <v>0</v>
+      </c>
+      <c r="AE90" s="24">
+        <v>1</v>
+      </c>
+      <c r="AF90" s="24">
+        <v>2</v>
+      </c>
+      <c r="AG90" s="21">
+        <v>0</v>
+      </c>
+      <c r="AH90" s="11"/>
+      <c r="AI90" s="11" t="s">
+        <v>635</v>
+      </c>
+      <c r="AJ90" s="11"/>
+      <c r="AK90" s="20" t="s">
+        <v>715</v>
       </c>
       <c r="AL90" t="s">
         <v>355</v>
       </c>
       <c r="AM90" t="s">
-        <v>59</v>
+        <v>100</v>
       </c>
     </row>
-    <row r="91" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>642</v>
-      </c>
-      <c r="B91" t="s">
-        <v>643</v>
-      </c>
-      <c r="C91" t="s">
-        <v>452</v>
+    <row r="91" spans="1:39" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A91" s="9" t="s">
+        <v>681</v>
+      </c>
+      <c r="B91" s="10" t="s">
+        <v>636</v>
+      </c>
+      <c r="C91" s="11" t="s">
+        <v>637</v>
       </c>
       <c r="D91" t="s">
         <v>41</v>
       </c>
       <c r="E91" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="F91" t="s">
         <v>42</v>
       </c>
       <c r="G91" t="s">
-        <v>104</v>
+        <v>63</v>
       </c>
       <c r="H91" t="s">
         <v>45</v>
       </c>
       <c r="I91" t="s">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="J91" t="s">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="K91" t="s">
-        <v>46</v>
-      </c>
-      <c r="L91" s="32" t="s">
-        <v>522</v>
+        <v>45</v>
+      </c>
+      <c r="L91" s="12" t="s">
+        <v>691</v>
       </c>
       <c r="M91" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="N91" t="s">
         <v>93</v>
@@ -13423,103 +13240,102 @@
       <c r="R91">
         <v>1</v>
       </c>
-      <c r="S91" s="8" t="s">
-        <v>465</v>
-      </c>
-      <c r="T91" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="U91" s="8" t="s">
-        <v>83</v>
+      <c r="S91" s="20" t="s">
+        <v>616</v>
+      </c>
+      <c r="T91" s="12" t="s">
+        <v>703</v>
+      </c>
+      <c r="U91" s="13" t="s">
+        <v>710</v>
       </c>
       <c r="V91" s="8">
-        <v>2</v>
-      </c>
-      <c r="W91" s="8">
-        <v>2</v>
-      </c>
-      <c r="X91" s="8">
-        <v>2</v>
-      </c>
-      <c r="AB91" s="7">
-        <v>3</v>
-      </c>
-      <c r="AC91" s="7">
-        <v>2</v>
-      </c>
-      <c r="AD91" s="7">
-        <v>1</v>
-      </c>
-      <c r="AE91" s="7">
-        <v>3</v>
-      </c>
-      <c r="AF91" s="7">
-        <v>2</v>
-      </c>
-      <c r="AG91">
-        <v>0</v>
-      </c>
-      <c r="AH91" t="s">
-        <v>624</v>
-      </c>
-      <c r="AI91" t="s">
-        <v>625</v>
-      </c>
-      <c r="AJ91" t="s">
-        <v>644</v>
-      </c>
-      <c r="AK91" t="s">
-        <v>119</v>
+        <v>1</v>
+      </c>
+      <c r="W91" s="13">
+        <v>1</v>
+      </c>
+      <c r="X91" s="13">
+        <v>1</v>
+      </c>
+      <c r="Y91" s="13"/>
+      <c r="AB91" s="23">
+        <v>2</v>
+      </c>
+      <c r="AC91" s="23">
+        <v>1</v>
+      </c>
+      <c r="AD91" s="23">
+        <v>1</v>
+      </c>
+      <c r="AE91" s="24">
+        <v>1</v>
+      </c>
+      <c r="AF91" s="24">
+        <v>2</v>
+      </c>
+      <c r="AG91" s="13">
+        <v>1</v>
+      </c>
+      <c r="AH91" s="17"/>
+      <c r="AI91" s="18" t="s">
+        <v>638</v>
+      </c>
+      <c r="AJ91" s="19" t="s">
+        <v>639</v>
+      </c>
+      <c r="AK91" s="20" t="s">
+        <v>713</v>
       </c>
       <c r="AL91" t="s">
         <v>355</v>
       </c>
       <c r="AM91" t="s">
-        <v>59</v>
+        <v>100</v>
       </c>
     </row>
-    <row r="92" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>645</v>
-      </c>
-      <c r="B92" t="s">
-        <v>646</v>
-      </c>
-      <c r="C92" t="s">
-        <v>647</v>
+    <row r="92" spans="1:39" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A92" s="9" t="s">
+        <v>682</v>
+      </c>
+      <c r="B92" s="10" t="s">
+        <v>640</v>
+      </c>
+      <c r="C92" s="11" t="s">
+        <v>641</v>
       </c>
       <c r="D92" t="s">
         <v>41</v>
       </c>
       <c r="E92" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="F92" t="s">
         <v>42</v>
       </c>
       <c r="G92" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="H92" t="s">
         <v>45</v>
       </c>
       <c r="I92" t="s">
-        <v>46</v>
+        <v>105</v>
       </c>
       <c r="J92" t="s">
-        <v>46</v>
+        <v>105</v>
       </c>
       <c r="K92" t="s">
-        <v>46</v>
-      </c>
-      <c r="L92" s="32" t="s">
-        <v>590</v>
+        <v>45</v>
+      </c>
+      <c r="L92" s="12" t="s">
+        <v>691</v>
       </c>
       <c r="M92" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="N92" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="O92" t="s">
         <v>107</v>
@@ -13533,70 +13349,69 @@
       <c r="R92">
         <v>1</v>
       </c>
-      <c r="S92" s="8" t="s">
-        <v>465</v>
-      </c>
-      <c r="T92" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="U92" s="8" t="s">
-        <v>648</v>
-      </c>
-      <c r="V92" s="8">
-        <v>3</v>
-      </c>
-      <c r="W92" s="8">
-        <v>2</v>
-      </c>
-      <c r="X92" s="8">
-        <v>0</v>
-      </c>
-      <c r="AB92" s="7">
-        <v>3</v>
-      </c>
-      <c r="AC92" s="7">
-        <v>2</v>
-      </c>
-      <c r="AD92" s="7">
-        <v>0</v>
-      </c>
-      <c r="AE92" s="7">
-        <v>3</v>
-      </c>
-      <c r="AF92" s="7">
-        <v>2</v>
-      </c>
-      <c r="AG92">
-        <v>0</v>
-      </c>
-      <c r="AH92" t="s">
-        <v>70</v>
-      </c>
-      <c r="AI92" t="s">
-        <v>448</v>
-      </c>
-      <c r="AJ92" t="s">
-        <v>649</v>
-      </c>
-      <c r="AK92" t="s">
-        <v>129</v>
+      <c r="S92" s="25">
+        <v>5</v>
+      </c>
+      <c r="T92" s="12" t="s">
+        <v>704</v>
+      </c>
+      <c r="U92" s="13" t="s">
+        <v>708</v>
+      </c>
+      <c r="V92" s="21">
+        <v>0</v>
+      </c>
+      <c r="W92" s="21">
+        <v>1</v>
+      </c>
+      <c r="X92" s="21">
+        <v>2</v>
+      </c>
+      <c r="Y92" s="21"/>
+      <c r="AB92" s="15">
+        <v>1</v>
+      </c>
+      <c r="AC92" s="15">
+        <v>2</v>
+      </c>
+      <c r="AD92" s="15">
+        <v>1</v>
+      </c>
+      <c r="AE92" s="22">
+        <v>1</v>
+      </c>
+      <c r="AF92" s="22">
+        <v>2</v>
+      </c>
+      <c r="AG92" s="21">
+        <v>1</v>
+      </c>
+      <c r="AH92" s="17"/>
+      <c r="AI92" s="18" t="s">
+        <v>642</v>
+      </c>
+      <c r="AJ92" s="19" t="s">
+        <v>643</v>
+      </c>
+      <c r="AK92" s="25">
+        <v>5</v>
       </c>
       <c r="AL92" t="s">
         <v>355</v>
       </c>
       <c r="AM92" t="s">
-        <v>59</v>
+        <v>100</v>
       </c>
     </row>
-    <row r="93" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>650</v>
-      </c>
-      <c r="B93" t="s">
-        <v>651</v>
-      </c>
-      <c r="C93" t="s">
-        <v>647</v>
+    <row r="93" spans="1:39" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A93" s="9" t="s">
+        <v>683</v>
+      </c>
+      <c r="B93" s="10" t="s">
+        <v>644</v>
+      </c>
+      <c r="C93" s="26" t="s">
+        <v>645</v>
       </c>
       <c r="D93" t="s">
         <v>41</v>
@@ -13608,25 +13423,25 @@
         <v>42</v>
       </c>
       <c r="G93" t="s">
-        <v>104</v>
+        <v>63</v>
       </c>
       <c r="H93" t="s">
         <v>45</v>
       </c>
       <c r="I93" t="s">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="J93" t="s">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="K93" t="s">
-        <v>46</v>
-      </c>
-      <c r="L93" s="32" t="s">
-        <v>652</v>
+        <v>45</v>
+      </c>
+      <c r="L93" s="12" t="s">
+        <v>694</v>
       </c>
       <c r="M93" t="s">
-        <v>491</v>
+        <v>464</v>
       </c>
       <c r="N93" t="s">
         <v>93</v>
@@ -13643,73 +13458,77 @@
       <c r="R93">
         <v>1</v>
       </c>
-      <c r="S93" s="8" t="s">
-        <v>465</v>
-      </c>
-      <c r="T93" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="U93" s="8" t="s">
-        <v>53</v>
+      <c r="S93" s="13">
+        <v>5</v>
+      </c>
+      <c r="T93" s="12" t="s">
+        <v>705</v>
+      </c>
+      <c r="U93" s="13" t="s">
+        <v>710</v>
       </c>
       <c r="V93" s="8">
         <v>2</v>
       </c>
-      <c r="W93" s="8">
-        <v>2</v>
-      </c>
-      <c r="X93" s="8">
-        <v>0</v>
-      </c>
-      <c r="AB93" s="7">
-        <v>3</v>
-      </c>
-      <c r="AC93" s="7">
-        <v>2</v>
-      </c>
-      <c r="AD93" s="7">
-        <v>0</v>
-      </c>
-      <c r="AE93" s="7">
-        <v>3</v>
-      </c>
-      <c r="AF93" s="7">
-        <v>2</v>
-      </c>
-      <c r="AG93">
-        <v>0</v>
-      </c>
-      <c r="AH93" t="s">
-        <v>70</v>
-      </c>
-      <c r="AI93" t="s">
-        <v>448</v>
-      </c>
-      <c r="AJ93" t="s">
-        <v>653</v>
-      </c>
-      <c r="AK93" t="s">
-        <v>119</v>
+      <c r="W93" s="13">
+        <v>1</v>
+      </c>
+      <c r="X93" s="13">
+        <v>1</v>
+      </c>
+      <c r="Y93" s="13"/>
+      <c r="AA93">
+        <v>2</v>
+      </c>
+      <c r="AB93" s="23">
+        <v>2</v>
+      </c>
+      <c r="AC93" s="23">
+        <v>1</v>
+      </c>
+      <c r="AD93" s="23">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="23">
+        <v>1</v>
+      </c>
+      <c r="AF93" s="22">
+        <v>2</v>
+      </c>
+      <c r="AG93" s="21">
+        <v>1</v>
+      </c>
+      <c r="AH93" s="27" t="s">
+        <v>646</v>
+      </c>
+      <c r="AI93" s="18" t="s">
+        <v>647</v>
+      </c>
+      <c r="AJ93" s="19" t="s">
+        <v>648</v>
+      </c>
+      <c r="AK93" s="13">
+        <v>5</v>
       </c>
       <c r="AL93" t="s">
         <v>355</v>
       </c>
       <c r="AM93" t="s">
-        <v>59</v>
+        <v>100</v>
       </c>
     </row>
-    <row r="94" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>654</v>
-      </c>
-      <c r="B94" t="s">
-        <v>655</v>
-      </c>
-      <c r="C94" t="s">
-        <v>457</v>
+    <row r="94" spans="1:39" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A94" s="9" t="s">
+        <v>684</v>
+      </c>
+      <c r="B94" s="10" t="s">
+        <v>649</v>
+      </c>
+      <c r="C94" s="11" t="s">
+        <v>650</v>
       </c>
       <c r="D94" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="E94" t="s">
         <v>42</v>
@@ -13718,28 +13537,28 @@
         <v>42</v>
       </c>
       <c r="G94" t="s">
-        <v>104</v>
+        <v>63</v>
       </c>
       <c r="H94" t="s">
         <v>45</v>
       </c>
       <c r="I94" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J94" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K94" t="s">
-        <v>46</v>
-      </c>
-      <c r="L94" s="32" t="s">
-        <v>210</v>
+        <v>45</v>
+      </c>
+      <c r="L94" s="12" t="s">
+        <v>695</v>
       </c>
       <c r="M94" t="s">
         <v>464</v>
       </c>
       <c r="N94" t="s">
-        <v>93</v>
+        <v>49</v>
       </c>
       <c r="O94" t="s">
         <v>107</v>
@@ -13753,103 +13572,102 @@
       <c r="R94">
         <v>1</v>
       </c>
-      <c r="S94" s="8" t="s">
-        <v>465</v>
-      </c>
-      <c r="T94" s="8" t="s">
-        <v>638</v>
-      </c>
-      <c r="U94" s="8" t="s">
-        <v>278</v>
+      <c r="S94" s="13">
+        <v>3</v>
+      </c>
+      <c r="T94" s="12" t="s">
+        <v>701</v>
+      </c>
+      <c r="U94" s="13" t="s">
+        <v>711</v>
       </c>
       <c r="V94" s="8">
         <v>1</v>
       </c>
-      <c r="W94" s="8">
-        <v>2</v>
-      </c>
-      <c r="X94" s="8">
-        <v>2</v>
-      </c>
-      <c r="AB94" s="7">
-        <v>3</v>
-      </c>
-      <c r="AC94" s="7">
-        <v>2</v>
-      </c>
-      <c r="AD94" s="7">
-        <v>0</v>
-      </c>
-      <c r="AE94" s="7">
-        <v>3</v>
-      </c>
-      <c r="AF94" s="7">
-        <v>2</v>
-      </c>
-      <c r="AG94">
-        <v>0</v>
-      </c>
-      <c r="AH94" t="s">
-        <v>70</v>
-      </c>
-      <c r="AI94" t="s">
-        <v>625</v>
-      </c>
-      <c r="AJ94" t="s">
-        <v>656</v>
-      </c>
-      <c r="AK94" t="s">
-        <v>217</v>
+      <c r="W94" s="14">
+        <v>1</v>
+      </c>
+      <c r="X94" s="14">
+        <v>1</v>
+      </c>
+      <c r="Y94" s="14"/>
+      <c r="AB94" s="15">
+        <v>1</v>
+      </c>
+      <c r="AC94" s="15">
+        <v>2</v>
+      </c>
+      <c r="AD94" s="15">
+        <v>1</v>
+      </c>
+      <c r="AE94" s="16">
+        <v>1</v>
+      </c>
+      <c r="AF94" s="16">
+        <v>2</v>
+      </c>
+      <c r="AG94" s="14">
+        <v>1</v>
+      </c>
+      <c r="AH94" s="17"/>
+      <c r="AI94" s="18" t="s">
+        <v>651</v>
+      </c>
+      <c r="AJ94" s="19" t="s">
+        <v>652</v>
+      </c>
+      <c r="AK94" s="13">
+        <v>3</v>
       </c>
       <c r="AL94" t="s">
         <v>355</v>
       </c>
       <c r="AM94" t="s">
-        <v>59</v>
+        <v>100</v>
       </c>
     </row>
-    <row r="95" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>657</v>
-      </c>
-      <c r="B95" t="s">
-        <v>658</v>
-      </c>
-      <c r="C95" t="s">
-        <v>659</v>
+    <row r="95" spans="1:39" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A95" s="9" t="s">
+        <v>685</v>
+      </c>
+      <c r="B95" s="10" t="s">
+        <v>653</v>
+      </c>
+      <c r="C95" s="11" t="s">
+        <v>654</v>
       </c>
       <c r="D95" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="E95" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F95" t="s">
         <v>42</v>
       </c>
       <c r="G95" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="H95" t="s">
         <v>45</v>
       </c>
       <c r="I95" t="s">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="J95" t="s">
-        <v>105</v>
+        <v>45</v>
       </c>
       <c r="K95" t="s">
-        <v>46</v>
-      </c>
-      <c r="L95" s="32" t="s">
-        <v>484</v>
+        <v>45</v>
+      </c>
+      <c r="L95" s="12" t="s">
+        <v>696</v>
       </c>
       <c r="M95" t="s">
-        <v>491</v>
+        <v>464</v>
       </c>
       <c r="N95" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="O95" t="s">
         <v>107</v>
@@ -13863,103 +13681,102 @@
       <c r="R95">
         <v>1</v>
       </c>
-      <c r="S95" s="8" t="s">
-        <v>465</v>
-      </c>
-      <c r="T95" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="U95" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="V95" s="8">
-        <v>0</v>
-      </c>
-      <c r="W95" s="8">
-        <v>2</v>
-      </c>
-      <c r="X95" s="8">
-        <v>3</v>
-      </c>
-      <c r="AB95" s="7">
-        <v>3</v>
-      </c>
-      <c r="AC95" s="7">
-        <v>2</v>
-      </c>
-      <c r="AD95" s="7">
-        <v>0</v>
-      </c>
-      <c r="AE95" s="7">
-        <v>3</v>
-      </c>
-      <c r="AF95" s="7">
-        <v>2</v>
-      </c>
-      <c r="AG95">
-        <v>0</v>
-      </c>
-      <c r="AH95" t="s">
-        <v>624</v>
-      </c>
-      <c r="AI95" t="s">
-        <v>660</v>
-      </c>
-      <c r="AJ95" t="s">
-        <v>661</v>
-      </c>
-      <c r="AK95" t="s">
-        <v>119</v>
+      <c r="S95" s="13">
+        <v>5</v>
+      </c>
+      <c r="T95" s="12" t="s">
+        <v>706</v>
+      </c>
+      <c r="U95" s="13" t="s">
+        <v>708</v>
+      </c>
+      <c r="V95" s="14">
+        <v>0</v>
+      </c>
+      <c r="W95" s="14">
+        <v>1</v>
+      </c>
+      <c r="X95" s="14">
+        <v>2</v>
+      </c>
+      <c r="Y95" s="14"/>
+      <c r="AB95" s="15">
+        <v>0</v>
+      </c>
+      <c r="AC95" s="15">
+        <v>1</v>
+      </c>
+      <c r="AD95" s="15">
+        <v>2</v>
+      </c>
+      <c r="AE95" s="16">
+        <v>2</v>
+      </c>
+      <c r="AF95" s="16">
+        <v>1</v>
+      </c>
+      <c r="AG95" s="14">
+        <v>0</v>
+      </c>
+      <c r="AH95" s="17"/>
+      <c r="AI95" s="18" t="s">
+        <v>655</v>
+      </c>
+      <c r="AJ95" s="19" t="s">
+        <v>656</v>
+      </c>
+      <c r="AK95" s="13">
+        <v>5</v>
       </c>
       <c r="AL95" t="s">
         <v>355</v>
       </c>
       <c r="AM95" t="s">
-        <v>59</v>
+        <v>100</v>
       </c>
     </row>
-    <row r="96" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>662</v>
-      </c>
-      <c r="B96" t="s">
-        <v>663</v>
-      </c>
-      <c r="C96" t="s">
-        <v>664</v>
+    <row r="96" spans="1:39" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A96" s="9" t="s">
+        <v>686</v>
+      </c>
+      <c r="B96" s="10" t="s">
+        <v>657</v>
+      </c>
+      <c r="C96" s="11" t="s">
+        <v>658</v>
       </c>
       <c r="D96" t="s">
+        <v>41</v>
+      </c>
+      <c r="E96" t="s">
         <v>63</v>
-      </c>
-      <c r="E96" t="s">
-        <v>42</v>
       </c>
       <c r="F96" t="s">
         <v>42</v>
       </c>
       <c r="G96" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="H96" t="s">
         <v>45</v>
       </c>
       <c r="I96" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J96" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K96" t="s">
-        <v>46</v>
-      </c>
-      <c r="L96" s="32" t="s">
-        <v>490</v>
+        <v>45</v>
+      </c>
+      <c r="L96" s="12" t="s">
+        <v>697</v>
       </c>
       <c r="M96" t="s">
-        <v>491</v>
+        <v>472</v>
       </c>
       <c r="N96" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="O96" t="s">
         <v>107</v>
@@ -13973,1708 +13790,496 @@
       <c r="R96">
         <v>1</v>
       </c>
-      <c r="S96" s="8" t="s">
-        <v>465</v>
-      </c>
-      <c r="T96" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="U96" s="8" t="s">
-        <v>53</v>
+      <c r="S96" s="28">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="T96" s="12" t="s">
+        <v>705</v>
+      </c>
+      <c r="U96" s="13" t="s">
+        <v>710</v>
       </c>
       <c r="V96" s="8">
-        <v>3</v>
-      </c>
-      <c r="W96" s="8">
-        <v>2</v>
-      </c>
-      <c r="X96" s="8">
-        <v>1</v>
-      </c>
-      <c r="AB96" s="7">
-        <v>1</v>
-      </c>
-      <c r="AC96" s="7">
-        <v>2</v>
-      </c>
-      <c r="AD96" s="7">
-        <v>0</v>
-      </c>
-      <c r="AE96" s="7">
-        <v>3</v>
-      </c>
-      <c r="AF96" s="7">
-        <v>2</v>
-      </c>
-      <c r="AG96">
-        <v>0</v>
-      </c>
-      <c r="AH96" t="s">
-        <v>70</v>
-      </c>
-      <c r="AI96" t="s">
-        <v>665</v>
-      </c>
-      <c r="AJ96" t="s">
-        <v>608</v>
-      </c>
-      <c r="AK96" t="s">
-        <v>57</v>
+        <v>1</v>
+      </c>
+      <c r="W96" s="14">
+        <v>2</v>
+      </c>
+      <c r="X96" s="14">
+        <v>2</v>
+      </c>
+      <c r="Y96" s="14"/>
+      <c r="Z96">
+        <v>2</v>
+      </c>
+      <c r="AB96" s="15">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="15">
+        <v>2</v>
+      </c>
+      <c r="AD96" s="15">
+        <v>1</v>
+      </c>
+      <c r="AE96" s="16">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="16">
+        <v>2</v>
+      </c>
+      <c r="AG96" s="14">
+        <v>1</v>
+      </c>
+      <c r="AH96" s="17"/>
+      <c r="AI96" s="18" t="s">
+        <v>659</v>
+      </c>
+      <c r="AJ96" s="19" t="s">
+        <v>660</v>
+      </c>
+      <c r="AK96" s="28">
+        <v>6</v>
       </c>
       <c r="AL96" t="s">
         <v>355</v>
       </c>
       <c r="AM96" t="s">
-        <v>59</v>
+        <v>100</v>
       </c>
     </row>
-    <row r="97" spans="1:39" s="12" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:39" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A97" s="9" t="s">
-        <v>734</v>
-      </c>
-      <c r="B97" s="10" t="s">
+        <v>687</v>
+      </c>
+      <c r="B97" s="29" t="s">
+        <v>661</v>
+      </c>
+      <c r="C97" s="11" t="s">
+        <v>662</v>
+      </c>
+      <c r="D97" t="s">
+        <v>63</v>
+      </c>
+      <c r="E97" t="s">
+        <v>42</v>
+      </c>
+      <c r="F97" t="s">
+        <v>42</v>
+      </c>
+      <c r="G97" t="s">
+        <v>63</v>
+      </c>
+      <c r="H97" t="s">
+        <v>45</v>
+      </c>
+      <c r="I97" t="s">
+        <v>45</v>
+      </c>
+      <c r="J97" t="s">
+        <v>45</v>
+      </c>
+      <c r="K97" t="s">
+        <v>45</v>
+      </c>
+      <c r="L97" s="24" t="s">
+        <v>471</v>
+      </c>
+      <c r="M97" t="s">
+        <v>472</v>
+      </c>
+      <c r="N97" t="s">
+        <v>66</v>
+      </c>
+      <c r="O97" t="s">
+        <v>107</v>
+      </c>
+      <c r="P97">
+        <v>0</v>
+      </c>
+      <c r="Q97">
+        <v>0</v>
+      </c>
+      <c r="R97">
+        <v>1</v>
+      </c>
+      <c r="S97" s="13">
+        <v>4</v>
+      </c>
+      <c r="T97" s="12" t="s">
+        <v>705</v>
+      </c>
+      <c r="U97" s="13" t="s">
+        <v>711</v>
+      </c>
+      <c r="V97" s="21">
+        <v>0</v>
+      </c>
+      <c r="W97" s="21">
+        <v>0</v>
+      </c>
+      <c r="X97" s="21">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="21"/>
+      <c r="AB97" s="15">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="15">
+        <v>2</v>
+      </c>
+      <c r="AD97" s="15">
+        <v>1</v>
+      </c>
+      <c r="AE97" s="22">
+        <v>0</v>
+      </c>
+      <c r="AF97" s="24">
+        <v>2</v>
+      </c>
+      <c r="AG97" s="13">
+        <v>1</v>
+      </c>
+      <c r="AH97" s="17"/>
+      <c r="AI97" s="17" t="s">
+        <v>663</v>
+      </c>
+      <c r="AJ97" s="19" t="s">
+        <v>664</v>
+      </c>
+      <c r="AK97" s="13">
+        <v>4</v>
+      </c>
+      <c r="AL97" t="s">
+        <v>355</v>
+      </c>
+      <c r="AM97" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="98" spans="1:39" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A98" s="9" t="s">
+        <v>688</v>
+      </c>
+      <c r="B98" s="29" t="s">
+        <v>665</v>
+      </c>
+      <c r="C98" s="11" t="s">
+        <v>666</v>
+      </c>
+      <c r="D98" t="s">
+        <v>63</v>
+      </c>
+      <c r="E98" t="s">
+        <v>42</v>
+      </c>
+      <c r="F98" t="s">
+        <v>42</v>
+      </c>
+      <c r="G98" t="s">
+        <v>63</v>
+      </c>
+      <c r="H98" t="s">
+        <v>45</v>
+      </c>
+      <c r="I98" t="s">
+        <v>45</v>
+      </c>
+      <c r="J98" t="s">
+        <v>45</v>
+      </c>
+      <c r="K98" t="s">
+        <v>45</v>
+      </c>
+      <c r="L98" s="12" t="s">
+        <v>698</v>
+      </c>
+      <c r="M98" t="s">
+        <v>472</v>
+      </c>
+      <c r="N98" t="s">
+        <v>93</v>
+      </c>
+      <c r="O98" t="s">
+        <v>107</v>
+      </c>
+      <c r="P98">
+        <v>0</v>
+      </c>
+      <c r="Q98">
+        <v>0</v>
+      </c>
+      <c r="R98">
+        <v>1</v>
+      </c>
+      <c r="S98" s="13">
+        <v>4</v>
+      </c>
+      <c r="T98" s="12" t="s">
+        <v>705</v>
+      </c>
+      <c r="U98" s="13" t="s">
+        <v>707</v>
+      </c>
+      <c r="V98" s="21">
+        <v>0</v>
+      </c>
+      <c r="W98" s="21">
+        <v>1</v>
+      </c>
+      <c r="X98" s="21">
+        <v>1</v>
+      </c>
+      <c r="Y98" s="21"/>
+      <c r="AB98" s="15">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="15">
+        <v>1</v>
+      </c>
+      <c r="AD98" s="15">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="22">
+        <v>1</v>
+      </c>
+      <c r="AF98" s="24">
+        <v>2</v>
+      </c>
+      <c r="AG98" s="13">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="17"/>
+      <c r="AI98" s="17" t="s">
         <v>667</v>
       </c>
-      <c r="C97" s="11" t="s">
+      <c r="AJ98" s="19"/>
+      <c r="AK98" s="13">
+        <v>4</v>
+      </c>
+      <c r="AL98" t="s">
+        <v>355</v>
+      </c>
+      <c r="AM98" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="99" spans="1:39" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A99" s="9" t="s">
+        <v>689</v>
+      </c>
+      <c r="B99" s="29" t="s">
         <v>668</v>
       </c>
-      <c r="D97" s="12" t="s">
+      <c r="C99" s="11" t="s">
+        <v>669</v>
+      </c>
+      <c r="D99" t="s">
         <v>63</v>
       </c>
-      <c r="E97" s="12" t="s">
+      <c r="E99" t="s">
         <v>42</v>
       </c>
-      <c r="F97" s="12" t="s">
+      <c r="F99" t="s">
         <v>42</v>
       </c>
-      <c r="G97" s="12" t="s">
+      <c r="G99" t="s">
         <v>63</v>
       </c>
-      <c r="H97" s="12" t="s">
+      <c r="H99" t="s">
         <v>45</v>
       </c>
-      <c r="I97" s="12" t="s">
+      <c r="I99" t="s">
         <v>45</v>
       </c>
-      <c r="J97" s="12" t="s">
+      <c r="J99" t="s">
         <v>45</v>
       </c>
-      <c r="K97" s="12" t="s">
+      <c r="K99" t="s">
         <v>45</v>
       </c>
-      <c r="L97" s="13" t="s">
-        <v>748</v>
-      </c>
-      <c r="M97" s="12" t="s">
+      <c r="L99" s="24" t="s">
+        <v>555</v>
+      </c>
+      <c r="M99" t="s">
+        <v>472</v>
+      </c>
+      <c r="N99" t="s">
+        <v>66</v>
+      </c>
+      <c r="O99" t="s">
+        <v>107</v>
+      </c>
+      <c r="P99">
+        <v>0</v>
+      </c>
+      <c r="Q99">
+        <v>0</v>
+      </c>
+      <c r="R99">
+        <v>1</v>
+      </c>
+      <c r="S99" s="13">
+        <v>4</v>
+      </c>
+      <c r="T99" s="12" t="s">
+        <v>701</v>
+      </c>
+      <c r="U99" s="13" t="s">
+        <v>709</v>
+      </c>
+      <c r="V99" s="8">
+        <v>1</v>
+      </c>
+      <c r="W99" s="13">
+        <v>2</v>
+      </c>
+      <c r="X99" s="13">
+        <v>1</v>
+      </c>
+      <c r="Y99" s="13"/>
+      <c r="AB99" s="23">
+        <v>1</v>
+      </c>
+      <c r="AC99" s="23">
+        <v>1</v>
+      </c>
+      <c r="AD99" s="23">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="24">
+        <v>2</v>
+      </c>
+      <c r="AF99" s="24">
+        <v>1</v>
+      </c>
+      <c r="AG99" s="21">
+        <v>1</v>
+      </c>
+      <c r="AH99" s="17"/>
+      <c r="AI99" s="17" t="s">
+        <v>670</v>
+      </c>
+      <c r="AJ99" s="19" t="s">
+        <v>671</v>
+      </c>
+      <c r="AK99" s="13">
+        <v>4</v>
+      </c>
+      <c r="AL99" t="s">
+        <v>355</v>
+      </c>
+      <c r="AM99" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="100" spans="1:39" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A100" s="9" t="s">
+        <v>690</v>
+      </c>
+      <c r="B100" s="10" t="s">
+        <v>672</v>
+      </c>
+      <c r="C100" s="11" t="s">
+        <v>673</v>
+      </c>
+      <c r="D100" t="s">
+        <v>41</v>
+      </c>
+      <c r="E100" t="s">
+        <v>63</v>
+      </c>
+      <c r="F100" t="s">
+        <v>42</v>
+      </c>
+      <c r="G100" t="s">
+        <v>63</v>
+      </c>
+      <c r="H100" t="s">
+        <v>45</v>
+      </c>
+      <c r="I100" t="s">
+        <v>45</v>
+      </c>
+      <c r="J100" t="s">
+        <v>45</v>
+      </c>
+      <c r="K100" t="s">
+        <v>45</v>
+      </c>
+      <c r="L100" s="12" t="s">
+        <v>696</v>
+      </c>
+      <c r="M100" t="s">
         <v>464</v>
       </c>
-      <c r="N97" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="O97" s="12" t="s">
+      <c r="N100" t="s">
+        <v>49</v>
+      </c>
+      <c r="O100" t="s">
         <v>107</v>
       </c>
-      <c r="P97" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q97" s="12">
-        <v>0</v>
-      </c>
-      <c r="R97" s="12">
-        <v>1</v>
-      </c>
-      <c r="S97" s="14">
+      <c r="P100">
+        <v>0</v>
+      </c>
+      <c r="Q100">
+        <v>0</v>
+      </c>
+      <c r="R100">
+        <v>1</v>
+      </c>
+      <c r="S100" s="13">
         <v>5</v>
       </c>
-      <c r="T97" s="13" t="s">
-        <v>756</v>
-      </c>
-      <c r="U97" s="14" t="s">
-        <v>764</v>
-      </c>
-      <c r="V97" s="15">
-        <v>1</v>
-      </c>
-      <c r="W97" s="16">
-        <v>2</v>
-      </c>
-      <c r="X97" s="16">
-        <v>1</v>
-      </c>
-      <c r="Y97" s="16"/>
-      <c r="AB97" s="17">
-        <v>1</v>
-      </c>
-      <c r="AC97" s="17">
-        <v>1</v>
-      </c>
-      <c r="AD97" s="17">
-        <v>0</v>
-      </c>
-      <c r="AE97" s="18">
-        <v>2</v>
-      </c>
-      <c r="AF97" s="18">
-        <v>1</v>
-      </c>
-      <c r="AG97" s="16">
-        <v>0</v>
-      </c>
-      <c r="AH97" s="19"/>
-      <c r="AI97" s="20" t="s">
-        <v>669</v>
-      </c>
-      <c r="AJ97" s="21" t="s">
-        <v>670</v>
-      </c>
-      <c r="AK97" s="14">
+      <c r="T100" s="12" t="s">
+        <v>700</v>
+      </c>
+      <c r="U100" s="13" t="s">
+        <v>712</v>
+      </c>
+      <c r="V100" s="14">
+        <v>0</v>
+      </c>
+      <c r="W100" s="14">
+        <v>2</v>
+      </c>
+      <c r="X100" s="14">
+        <v>1</v>
+      </c>
+      <c r="Y100" s="14"/>
+      <c r="AB100" s="15">
+        <v>1</v>
+      </c>
+      <c r="AC100" s="15">
+        <v>2</v>
+      </c>
+      <c r="AD100" s="15">
+        <v>1</v>
+      </c>
+      <c r="AE100" s="16">
+        <v>1</v>
+      </c>
+      <c r="AF100" s="16">
+        <v>2</v>
+      </c>
+      <c r="AG100" s="14">
+        <v>1</v>
+      </c>
+      <c r="AH100" s="17" t="s">
+        <v>674</v>
+      </c>
+      <c r="AI100" s="18" t="s">
+        <v>675</v>
+      </c>
+      <c r="AJ100" s="19" t="s">
+        <v>676</v>
+      </c>
+      <c r="AK100" s="13">
         <v>5</v>
       </c>
-      <c r="AL97" s="12" t="s">
+      <c r="AL100" t="s">
         <v>355</v>
       </c>
-      <c r="AM97" s="12" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="98" spans="1:39" s="12" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="9" t="s">
-        <v>735</v>
-      </c>
-      <c r="B98" s="10" t="s">
-        <v>671</v>
-      </c>
-      <c r="C98" s="11" t="s">
-        <v>672</v>
-      </c>
-      <c r="D98" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="E98" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F98" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G98" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="H98" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I98" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="J98" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="K98" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="L98" s="13" t="s">
-        <v>749</v>
-      </c>
-      <c r="M98" s="12" t="s">
-        <v>464</v>
-      </c>
-      <c r="N98" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="O98" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="P98" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q98" s="12">
-        <v>0</v>
-      </c>
-      <c r="R98" s="12">
-        <v>1</v>
-      </c>
-      <c r="S98" s="22" t="s">
-        <v>673</v>
-      </c>
-      <c r="T98" s="13" t="s">
-        <v>757</v>
-      </c>
-      <c r="U98" s="14" t="s">
-        <v>765</v>
-      </c>
-      <c r="V98" s="23">
-        <v>0</v>
-      </c>
-      <c r="W98" s="23">
-        <v>1</v>
-      </c>
-      <c r="X98" s="23">
-        <v>2</v>
-      </c>
-      <c r="Y98" s="23"/>
-      <c r="AB98" s="17">
-        <v>1</v>
-      </c>
-      <c r="AC98" s="17">
-        <v>2</v>
-      </c>
-      <c r="AD98" s="17">
-        <v>1</v>
-      </c>
-      <c r="AE98" s="24">
-        <v>2</v>
-      </c>
-      <c r="AF98" s="24">
-        <v>1</v>
-      </c>
-      <c r="AG98" s="23">
-        <v>1</v>
-      </c>
-      <c r="AH98" s="19" t="s">
-        <v>674</v>
-      </c>
-      <c r="AI98" s="20" t="s">
-        <v>675</v>
-      </c>
-      <c r="AJ98" s="21" t="s">
-        <v>676</v>
-      </c>
-      <c r="AK98" s="22" t="s">
-        <v>770</v>
-      </c>
-      <c r="AL98" s="12" t="s">
-        <v>355</v>
-      </c>
-      <c r="AM98" s="12" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="99" spans="1:39" s="12" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="9" t="s">
-        <v>736</v>
-      </c>
-      <c r="B99" s="10" t="s">
-        <v>677</v>
-      </c>
-      <c r="C99" s="11" t="s">
-        <v>678</v>
-      </c>
-      <c r="D99" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="E99" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F99" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G99" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="H99" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I99" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="J99" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="K99" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="L99" s="13" t="s">
-        <v>750</v>
-      </c>
-      <c r="M99" s="12" t="s">
-        <v>464</v>
-      </c>
-      <c r="N99" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="O99" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="P99" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q99" s="12">
-        <v>0</v>
-      </c>
-      <c r="R99" s="12">
-        <v>1</v>
-      </c>
-      <c r="S99" s="22" t="s">
-        <v>679</v>
-      </c>
-      <c r="T99" s="13" t="s">
-        <v>758</v>
-      </c>
-      <c r="U99" s="14" t="s">
-        <v>766</v>
-      </c>
-      <c r="V99" s="15">
-        <v>1</v>
-      </c>
-      <c r="W99" s="14">
-        <v>1</v>
-      </c>
-      <c r="X99" s="14">
-        <v>2</v>
-      </c>
-      <c r="Y99" s="14"/>
-      <c r="AB99" s="25">
-        <v>0</v>
-      </c>
-      <c r="AC99" s="25">
-        <v>1</v>
-      </c>
-      <c r="AD99" s="25">
-        <v>2</v>
-      </c>
-      <c r="AE99" s="26">
-        <v>2</v>
-      </c>
-      <c r="AF99" s="26">
-        <v>1</v>
-      </c>
-      <c r="AG99" s="14">
-        <v>1</v>
-      </c>
-      <c r="AH99" s="19" t="s">
-        <v>680</v>
-      </c>
-      <c r="AI99" s="20" t="s">
-        <v>681</v>
-      </c>
-      <c r="AJ99" s="21" t="s">
-        <v>682</v>
-      </c>
-      <c r="AK99" s="22" t="s">
-        <v>771</v>
-      </c>
-      <c r="AL99" s="12" t="s">
-        <v>355</v>
-      </c>
-      <c r="AM99" s="12" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="100" spans="1:39" s="12" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="9" t="s">
-        <v>737</v>
-      </c>
-      <c r="B100" s="10" t="s">
-        <v>683</v>
-      </c>
-      <c r="C100" s="11" t="s">
-        <v>684</v>
-      </c>
-      <c r="D100" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="E100" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F100" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G100" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="H100" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I100" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="J100" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="K100" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="L100" s="13" t="s">
-        <v>773</v>
-      </c>
-      <c r="M100" s="12" t="s">
-        <v>491</v>
-      </c>
-      <c r="N100" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="O100" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="P100" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q100" s="12">
-        <v>0</v>
-      </c>
-      <c r="R100" s="12">
-        <v>1</v>
-      </c>
-      <c r="S100" s="14">
-        <v>5</v>
-      </c>
-      <c r="T100" s="13" t="s">
-        <v>757</v>
-      </c>
-      <c r="U100" s="14" t="s">
-        <v>765</v>
-      </c>
-      <c r="V100" s="14">
-        <v>0</v>
-      </c>
-      <c r="W100" s="14">
-        <v>1</v>
-      </c>
-      <c r="X100" s="14">
-        <v>2</v>
-      </c>
-      <c r="Y100" s="14"/>
-      <c r="Z100" s="12">
-        <v>2</v>
-      </c>
-      <c r="AB100" s="25">
-        <v>0</v>
-      </c>
-      <c r="AC100" s="25">
-        <v>1</v>
-      </c>
-      <c r="AD100" s="25">
-        <v>2</v>
-      </c>
-      <c r="AE100" s="26">
-        <v>2</v>
-      </c>
-      <c r="AF100" s="26">
-        <v>1</v>
-      </c>
-      <c r="AG100" s="14">
-        <v>0</v>
-      </c>
-      <c r="AH100" s="19" t="s">
-        <v>685</v>
-      </c>
-      <c r="AI100" s="20" t="s">
-        <v>686</v>
-      </c>
-      <c r="AJ100" s="21" t="s">
-        <v>687</v>
-      </c>
-      <c r="AK100" s="14">
-        <v>5</v>
-      </c>
-      <c r="AL100" s="12" t="s">
-        <v>355</v>
-      </c>
-      <c r="AM100" s="12" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="101" spans="1:39" s="12" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="11" t="s">
-        <v>688</v>
-      </c>
-      <c r="B101" s="10" t="s">
-        <v>689</v>
-      </c>
-      <c r="C101" s="11" t="s">
-        <v>690</v>
-      </c>
-      <c r="D101" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="E101" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F101" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G101" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="H101" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I101" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="J101" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="K101" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="L101" s="26" t="s">
-        <v>490</v>
-      </c>
-      <c r="M101" s="12" t="s">
-        <v>491</v>
-      </c>
-      <c r="N101" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="O101" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="P101" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="12">
-        <v>0</v>
-      </c>
-      <c r="R101" s="12">
-        <v>1</v>
-      </c>
-      <c r="S101" s="22" t="s">
-        <v>691</v>
-      </c>
-      <c r="T101" s="26" t="s">
-        <v>759</v>
-      </c>
-      <c r="U101" s="14" t="s">
-        <v>767</v>
-      </c>
-      <c r="V101" s="14">
-        <v>1</v>
-      </c>
-      <c r="W101" s="14">
-        <v>1</v>
-      </c>
-      <c r="X101" s="14">
-        <v>1</v>
-      </c>
-      <c r="Y101" s="14"/>
-      <c r="AB101" s="26">
-        <v>0</v>
-      </c>
-      <c r="AC101" s="26">
-        <v>1</v>
-      </c>
-      <c r="AD101" s="26">
-        <v>0</v>
-      </c>
-      <c r="AE101" s="26">
-        <v>1</v>
-      </c>
-      <c r="AF101" s="26">
-        <v>2</v>
-      </c>
-      <c r="AG101" s="23">
-        <v>0</v>
-      </c>
-      <c r="AH101" s="11"/>
-      <c r="AI101" s="11" t="s">
-        <v>692</v>
-      </c>
-      <c r="AJ101" s="11"/>
-      <c r="AK101" s="22" t="s">
-        <v>772</v>
-      </c>
-      <c r="AL101" s="12" t="s">
-        <v>355</v>
-      </c>
-      <c r="AM101" s="12" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="102" spans="1:39" s="12" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="9" t="s">
-        <v>738</v>
-      </c>
-      <c r="B102" s="10" t="s">
-        <v>693</v>
-      </c>
-      <c r="C102" s="11" t="s">
-        <v>694</v>
-      </c>
-      <c r="D102" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="E102" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="F102" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G102" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="H102" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I102" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="J102" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="K102" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="L102" s="13" t="s">
-        <v>748</v>
-      </c>
-      <c r="M102" s="12" t="s">
-        <v>491</v>
-      </c>
-      <c r="N102" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="O102" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="P102" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="12">
-        <v>0</v>
-      </c>
-      <c r="R102" s="12">
-        <v>1</v>
-      </c>
-      <c r="S102" s="22" t="s">
-        <v>673</v>
-      </c>
-      <c r="T102" s="13" t="s">
-        <v>760</v>
-      </c>
-      <c r="U102" s="14" t="s">
-        <v>767</v>
-      </c>
-      <c r="V102" s="15">
-        <v>1</v>
-      </c>
-      <c r="W102" s="14">
-        <v>1</v>
-      </c>
-      <c r="X102" s="14">
-        <v>1</v>
-      </c>
-      <c r="Y102" s="14"/>
-      <c r="AB102" s="25">
-        <v>2</v>
-      </c>
-      <c r="AC102" s="25">
-        <v>1</v>
-      </c>
-      <c r="AD102" s="25">
-        <v>1</v>
-      </c>
-      <c r="AE102" s="26">
-        <v>1</v>
-      </c>
-      <c r="AF102" s="26">
-        <v>2</v>
-      </c>
-      <c r="AG102" s="14">
-        <v>1</v>
-      </c>
-      <c r="AH102" s="19"/>
-      <c r="AI102" s="20" t="s">
-        <v>695</v>
-      </c>
-      <c r="AJ102" s="21" t="s">
-        <v>696</v>
-      </c>
-      <c r="AK102" s="22" t="s">
-        <v>770</v>
-      </c>
-      <c r="AL102" s="12" t="s">
-        <v>355</v>
-      </c>
-      <c r="AM102" s="12" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="103" spans="1:39" s="12" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="9" t="s">
-        <v>739</v>
-      </c>
-      <c r="B103" s="10" t="s">
-        <v>697</v>
-      </c>
-      <c r="C103" s="11" t="s">
-        <v>698</v>
-      </c>
-      <c r="D103" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="E103" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="F103" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G103" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="H103" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I103" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="J103" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="K103" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="L103" s="13" t="s">
-        <v>748</v>
-      </c>
-      <c r="M103" s="12" t="s">
-        <v>491</v>
-      </c>
-      <c r="N103" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="O103" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="P103" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q103" s="12">
-        <v>0</v>
-      </c>
-      <c r="R103" s="12">
-        <v>1</v>
-      </c>
-      <c r="S103" s="27">
-        <v>5</v>
-      </c>
-      <c r="T103" s="13" t="s">
-        <v>761</v>
-      </c>
-      <c r="U103" s="14" t="s">
-        <v>765</v>
-      </c>
-      <c r="V103" s="23">
-        <v>0</v>
-      </c>
-      <c r="W103" s="23">
-        <v>1</v>
-      </c>
-      <c r="X103" s="23">
-        <v>2</v>
-      </c>
-      <c r="Y103" s="23"/>
-      <c r="AB103" s="17">
-        <v>1</v>
-      </c>
-      <c r="AC103" s="17">
-        <v>2</v>
-      </c>
-      <c r="AD103" s="17">
-        <v>1</v>
-      </c>
-      <c r="AE103" s="24">
-        <v>1</v>
-      </c>
-      <c r="AF103" s="24">
-        <v>2</v>
-      </c>
-      <c r="AG103" s="23">
-        <v>1</v>
-      </c>
-      <c r="AH103" s="19"/>
-      <c r="AI103" s="20" t="s">
-        <v>699</v>
-      </c>
-      <c r="AJ103" s="21" t="s">
-        <v>700</v>
-      </c>
-      <c r="AK103" s="27">
-        <v>5</v>
-      </c>
-      <c r="AL103" s="12" t="s">
-        <v>355</v>
-      </c>
-      <c r="AM103" s="12" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="104" spans="1:39" s="12" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="9" t="s">
-        <v>740</v>
-      </c>
-      <c r="B104" s="10" t="s">
-        <v>701</v>
-      </c>
-      <c r="C104" s="28" t="s">
-        <v>702</v>
-      </c>
-      <c r="D104" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="E104" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F104" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G104" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="H104" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I104" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="J104" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="K104" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="L104" s="13" t="s">
-        <v>751</v>
-      </c>
-      <c r="M104" s="12" t="s">
-        <v>464</v>
-      </c>
-      <c r="N104" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="O104" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="P104" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q104" s="12">
-        <v>0</v>
-      </c>
-      <c r="R104" s="12">
-        <v>1</v>
-      </c>
-      <c r="S104" s="14">
-        <v>5</v>
-      </c>
-      <c r="T104" s="13" t="s">
-        <v>762</v>
-      </c>
-      <c r="U104" s="14" t="s">
-        <v>767</v>
-      </c>
-      <c r="V104" s="15">
-        <v>2</v>
-      </c>
-      <c r="W104" s="14">
-        <v>1</v>
-      </c>
-      <c r="X104" s="14">
-        <v>1</v>
-      </c>
-      <c r="Y104" s="14"/>
-      <c r="AA104" s="12">
-        <v>2</v>
-      </c>
-      <c r="AB104" s="25">
-        <v>2</v>
-      </c>
-      <c r="AC104" s="25">
-        <v>1</v>
-      </c>
-      <c r="AD104" s="25">
-        <v>0</v>
-      </c>
-      <c r="AE104" s="25">
-        <v>1</v>
-      </c>
-      <c r="AF104" s="24">
-        <v>2</v>
-      </c>
-      <c r="AG104" s="23">
-        <v>1</v>
-      </c>
-      <c r="AH104" s="29" t="s">
-        <v>703</v>
-      </c>
-      <c r="AI104" s="20" t="s">
-        <v>704</v>
-      </c>
-      <c r="AJ104" s="21" t="s">
-        <v>705</v>
-      </c>
-      <c r="AK104" s="14">
-        <v>5</v>
-      </c>
-      <c r="AL104" s="12" t="s">
-        <v>355</v>
-      </c>
-      <c r="AM104" s="12" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="105" spans="1:39" s="12" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="9" t="s">
-        <v>741</v>
-      </c>
-      <c r="B105" s="10" t="s">
-        <v>706</v>
-      </c>
-      <c r="C105" s="11" t="s">
-        <v>707</v>
-      </c>
-      <c r="D105" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="E105" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F105" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G105" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="H105" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I105" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="J105" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="K105" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="L105" s="13" t="s">
-        <v>752</v>
-      </c>
-      <c r="M105" s="12" t="s">
-        <v>464</v>
-      </c>
-      <c r="N105" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="O105" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="P105" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q105" s="12">
-        <v>0</v>
-      </c>
-      <c r="R105" s="12">
-        <v>1</v>
-      </c>
-      <c r="S105" s="14">
-        <v>3</v>
-      </c>
-      <c r="T105" s="13" t="s">
-        <v>758</v>
-      </c>
-      <c r="U105" s="14" t="s">
-        <v>768</v>
-      </c>
-      <c r="V105" s="15">
-        <v>1</v>
-      </c>
-      <c r="W105" s="16">
-        <v>1</v>
-      </c>
-      <c r="X105" s="16">
-        <v>1</v>
-      </c>
-      <c r="Y105" s="16"/>
-      <c r="AB105" s="17">
-        <v>1</v>
-      </c>
-      <c r="AC105" s="17">
-        <v>2</v>
-      </c>
-      <c r="AD105" s="17">
-        <v>1</v>
-      </c>
-      <c r="AE105" s="18">
-        <v>1</v>
-      </c>
-      <c r="AF105" s="18">
-        <v>2</v>
-      </c>
-      <c r="AG105" s="16">
-        <v>1</v>
-      </c>
-      <c r="AH105" s="19"/>
-      <c r="AI105" s="20" t="s">
-        <v>708</v>
-      </c>
-      <c r="AJ105" s="21" t="s">
-        <v>709</v>
-      </c>
-      <c r="AK105" s="14">
-        <v>3</v>
-      </c>
-      <c r="AL105" s="12" t="s">
-        <v>355</v>
-      </c>
-      <c r="AM105" s="12" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="106" spans="1:39" s="12" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="9" t="s">
-        <v>742</v>
-      </c>
-      <c r="B106" s="10" t="s">
-        <v>710</v>
-      </c>
-      <c r="C106" s="11" t="s">
-        <v>711</v>
-      </c>
-      <c r="D106" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="E106" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F106" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G106" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="H106" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I106" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="J106" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="K106" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="L106" s="13" t="s">
-        <v>753</v>
-      </c>
-      <c r="M106" s="12" t="s">
-        <v>464</v>
-      </c>
-      <c r="N106" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="O106" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="P106" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q106" s="12">
-        <v>0</v>
-      </c>
-      <c r="R106" s="12">
-        <v>1</v>
-      </c>
-      <c r="S106" s="14">
-        <v>5</v>
-      </c>
-      <c r="T106" s="13" t="s">
-        <v>763</v>
-      </c>
-      <c r="U106" s="14" t="s">
-        <v>765</v>
-      </c>
-      <c r="V106" s="16">
-        <v>0</v>
-      </c>
-      <c r="W106" s="16">
-        <v>1</v>
-      </c>
-      <c r="X106" s="16">
-        <v>2</v>
-      </c>
-      <c r="Y106" s="16"/>
-      <c r="AB106" s="17">
-        <v>0</v>
-      </c>
-      <c r="AC106" s="17">
-        <v>1</v>
-      </c>
-      <c r="AD106" s="17">
-        <v>2</v>
-      </c>
-      <c r="AE106" s="18">
-        <v>2</v>
-      </c>
-      <c r="AF106" s="18">
-        <v>1</v>
-      </c>
-      <c r="AG106" s="16">
-        <v>0</v>
-      </c>
-      <c r="AH106" s="19"/>
-      <c r="AI106" s="20" t="s">
-        <v>712</v>
-      </c>
-      <c r="AJ106" s="21" t="s">
-        <v>713</v>
-      </c>
-      <c r="AK106" s="14">
-        <v>5</v>
-      </c>
-      <c r="AL106" s="12" t="s">
-        <v>355</v>
-      </c>
-      <c r="AM106" s="12" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="107" spans="1:39" s="12" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="9" t="s">
-        <v>743</v>
-      </c>
-      <c r="B107" s="10" t="s">
-        <v>714</v>
-      </c>
-      <c r="C107" s="11" t="s">
-        <v>715</v>
-      </c>
-      <c r="D107" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="E107" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="F107" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G107" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="H107" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I107" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="J107" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="K107" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="L107" s="13" t="s">
-        <v>754</v>
-      </c>
-      <c r="M107" s="12" t="s">
-        <v>491</v>
-      </c>
-      <c r="N107" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="O107" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="P107" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q107" s="12">
-        <v>0</v>
-      </c>
-      <c r="R107" s="12">
-        <v>1</v>
-      </c>
-      <c r="S107" s="30">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="T107" s="13" t="s">
-        <v>762</v>
-      </c>
-      <c r="U107" s="14" t="s">
-        <v>767</v>
-      </c>
-      <c r="V107" s="15">
-        <v>1</v>
-      </c>
-      <c r="W107" s="16">
-        <v>2</v>
-      </c>
-      <c r="X107" s="16">
-        <v>2</v>
-      </c>
-      <c r="Y107" s="16"/>
-      <c r="Z107" s="12">
-        <v>2</v>
-      </c>
-      <c r="AB107" s="17">
-        <v>0</v>
-      </c>
-      <c r="AC107" s="17">
-        <v>2</v>
-      </c>
-      <c r="AD107" s="17">
-        <v>1</v>
-      </c>
-      <c r="AE107" s="18">
-        <v>0</v>
-      </c>
-      <c r="AF107" s="18">
-        <v>2</v>
-      </c>
-      <c r="AG107" s="16">
-        <v>1</v>
-      </c>
-      <c r="AH107" s="19"/>
-      <c r="AI107" s="20" t="s">
-        <v>716</v>
-      </c>
-      <c r="AJ107" s="21" t="s">
-        <v>717</v>
-      </c>
-      <c r="AK107" s="30">
-        <v>6</v>
-      </c>
-      <c r="AL107" s="12" t="s">
-        <v>355</v>
-      </c>
-      <c r="AM107" s="12" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="108" spans="1:39" s="12" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="9" t="s">
-        <v>744</v>
-      </c>
-      <c r="B108" s="31" t="s">
-        <v>718</v>
-      </c>
-      <c r="C108" s="11" t="s">
-        <v>719</v>
-      </c>
-      <c r="D108" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="E108" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F108" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G108" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="H108" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I108" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="J108" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="K108" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="L108" s="26" t="s">
-        <v>490</v>
-      </c>
-      <c r="M108" s="12" t="s">
-        <v>491</v>
-      </c>
-      <c r="N108" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="O108" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="P108" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q108" s="12">
-        <v>0</v>
-      </c>
-      <c r="R108" s="12">
-        <v>1</v>
-      </c>
-      <c r="S108" s="14">
-        <v>4</v>
-      </c>
-      <c r="T108" s="13" t="s">
-        <v>762</v>
-      </c>
-      <c r="U108" s="14" t="s">
-        <v>768</v>
-      </c>
-      <c r="V108" s="23">
-        <v>0</v>
-      </c>
-      <c r="W108" s="23">
-        <v>0</v>
-      </c>
-      <c r="X108" s="23">
-        <v>0</v>
-      </c>
-      <c r="Y108" s="23"/>
-      <c r="AB108" s="17">
-        <v>0</v>
-      </c>
-      <c r="AC108" s="17">
-        <v>2</v>
-      </c>
-      <c r="AD108" s="17">
-        <v>1</v>
-      </c>
-      <c r="AE108" s="24">
-        <v>0</v>
-      </c>
-      <c r="AF108" s="26">
-        <v>2</v>
-      </c>
-      <c r="AG108" s="14">
-        <v>1</v>
-      </c>
-      <c r="AH108" s="19"/>
-      <c r="AI108" s="19" t="s">
-        <v>720</v>
-      </c>
-      <c r="AJ108" s="21" t="s">
-        <v>721</v>
-      </c>
-      <c r="AK108" s="14">
-        <v>4</v>
-      </c>
-      <c r="AL108" s="12" t="s">
-        <v>355</v>
-      </c>
-      <c r="AM108" s="12" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="109" spans="1:39" s="12" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="9" t="s">
-        <v>745</v>
-      </c>
-      <c r="B109" s="31" t="s">
-        <v>722</v>
-      </c>
-      <c r="C109" s="11" t="s">
-        <v>723</v>
-      </c>
-      <c r="D109" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="E109" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F109" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G109" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="H109" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I109" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="J109" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="K109" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="L109" s="13" t="s">
-        <v>755</v>
-      </c>
-      <c r="M109" s="12" t="s">
-        <v>491</v>
-      </c>
-      <c r="N109" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="O109" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="P109" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q109" s="12">
-        <v>0</v>
-      </c>
-      <c r="R109" s="12">
-        <v>1</v>
-      </c>
-      <c r="S109" s="14">
-        <v>4</v>
-      </c>
-      <c r="T109" s="13" t="s">
-        <v>762</v>
-      </c>
-      <c r="U109" s="14" t="s">
-        <v>764</v>
-      </c>
-      <c r="V109" s="23">
-        <v>0</v>
-      </c>
-      <c r="W109" s="23">
-        <v>1</v>
-      </c>
-      <c r="X109" s="23">
-        <v>1</v>
-      </c>
-      <c r="Y109" s="23"/>
-      <c r="AB109" s="17">
-        <v>0</v>
-      </c>
-      <c r="AC109" s="17">
-        <v>1</v>
-      </c>
-      <c r="AD109" s="17">
-        <v>0</v>
-      </c>
-      <c r="AE109" s="24">
-        <v>1</v>
-      </c>
-      <c r="AF109" s="26">
-        <v>2</v>
-      </c>
-      <c r="AG109" s="14">
-        <v>0</v>
-      </c>
-      <c r="AH109" s="19"/>
-      <c r="AI109" s="19" t="s">
-        <v>724</v>
-      </c>
-      <c r="AJ109" s="21"/>
-      <c r="AK109" s="14">
-        <v>4</v>
-      </c>
-      <c r="AL109" s="12" t="s">
-        <v>355</v>
-      </c>
-      <c r="AM109" s="12" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="110" spans="1:39" s="12" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="9" t="s">
-        <v>746</v>
-      </c>
-      <c r="B110" s="31" t="s">
-        <v>725</v>
-      </c>
-      <c r="C110" s="11" t="s">
-        <v>726</v>
-      </c>
-      <c r="D110" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="E110" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F110" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G110" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="H110" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I110" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="J110" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="K110" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="L110" s="26" t="s">
-        <v>607</v>
-      </c>
-      <c r="M110" s="12" t="s">
-        <v>491</v>
-      </c>
-      <c r="N110" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="O110" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="P110" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q110" s="12">
-        <v>0</v>
-      </c>
-      <c r="R110" s="12">
-        <v>1</v>
-      </c>
-      <c r="S110" s="14">
-        <v>4</v>
-      </c>
-      <c r="T110" s="13" t="s">
-        <v>758</v>
-      </c>
-      <c r="U110" s="14" t="s">
-        <v>766</v>
-      </c>
-      <c r="V110" s="15">
-        <v>1</v>
-      </c>
-      <c r="W110" s="14">
-        <v>2</v>
-      </c>
-      <c r="X110" s="14">
-        <v>1</v>
-      </c>
-      <c r="Y110" s="14"/>
-      <c r="AB110" s="25">
-        <v>1</v>
-      </c>
-      <c r="AC110" s="25">
-        <v>1</v>
-      </c>
-      <c r="AD110" s="25">
-        <v>0</v>
-      </c>
-      <c r="AE110" s="26">
-        <v>2</v>
-      </c>
-      <c r="AF110" s="26">
-        <v>1</v>
-      </c>
-      <c r="AG110" s="23">
-        <v>1</v>
-      </c>
-      <c r="AH110" s="19"/>
-      <c r="AI110" s="19" t="s">
-        <v>727</v>
-      </c>
-      <c r="AJ110" s="21" t="s">
-        <v>728</v>
-      </c>
-      <c r="AK110" s="14">
-        <v>4</v>
-      </c>
-      <c r="AL110" s="12" t="s">
-        <v>355</v>
-      </c>
-      <c r="AM110" s="12" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="111" spans="1:39" s="12" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="9" t="s">
-        <v>747</v>
-      </c>
-      <c r="B111" s="10" t="s">
-        <v>729</v>
-      </c>
-      <c r="C111" s="11" t="s">
-        <v>730</v>
-      </c>
-      <c r="D111" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="E111" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="F111" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G111" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="H111" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="I111" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="J111" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="K111" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="L111" s="13" t="s">
-        <v>753</v>
-      </c>
-      <c r="M111" s="12" t="s">
-        <v>464</v>
-      </c>
-      <c r="N111" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="O111" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="P111" s="12">
-        <v>0</v>
-      </c>
-      <c r="Q111" s="12">
-        <v>0</v>
-      </c>
-      <c r="R111" s="12">
-        <v>1</v>
-      </c>
-      <c r="S111" s="14">
-        <v>5</v>
-      </c>
-      <c r="T111" s="13" t="s">
-        <v>757</v>
-      </c>
-      <c r="U111" s="14" t="s">
-        <v>769</v>
-      </c>
-      <c r="V111" s="16">
-        <v>0</v>
-      </c>
-      <c r="W111" s="16">
-        <v>2</v>
-      </c>
-      <c r="X111" s="16">
-        <v>1</v>
-      </c>
-      <c r="Y111" s="16"/>
-      <c r="AB111" s="17">
-        <v>1</v>
-      </c>
-      <c r="AC111" s="17">
-        <v>2</v>
-      </c>
-      <c r="AD111" s="17">
-        <v>1</v>
-      </c>
-      <c r="AE111" s="18">
-        <v>1</v>
-      </c>
-      <c r="AF111" s="18">
-        <v>2</v>
-      </c>
-      <c r="AG111" s="16">
-        <v>1</v>
-      </c>
-      <c r="AH111" s="19" t="s">
-        <v>731</v>
-      </c>
-      <c r="AI111" s="20" t="s">
-        <v>732</v>
-      </c>
-      <c r="AJ111" s="21" t="s">
-        <v>733</v>
-      </c>
-      <c r="AK111" s="14">
-        <v>5</v>
-      </c>
-      <c r="AL111" s="12" t="s">
-        <v>355</v>
-      </c>
-      <c r="AM111" s="12" t="s">
+      <c r="AM100" t="s">
         <v>100</v>
       </c>
     </row>
@@ -15693,63 +14298,63 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06060BC5-9F75-40DD-8F4D-4DCE3296265C}">
   <dimension ref="N1:N17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="14" width="8.140625" customWidth="1"/>
-    <col min="15" max="15" width="27.85546875" customWidth="1"/>
+    <col min="1" max="14" width="8.1328125" customWidth="1"/>
+    <col min="15" max="15" width="27.86328125" customWidth="1"/>
     <col min="16" max="16" width="47" customWidth="1"/>
     <col min="17" max="17" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N1" s="1"/>
     </row>
-    <row r="2" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N2" s="2"/>
     </row>
-    <row r="3" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N3" s="3"/>
     </row>
-    <row r="4" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N4" s="3"/>
     </row>
-    <row r="5" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N5" s="3"/>
     </row>
-    <row r="6" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N6" s="3"/>
     </row>
-    <row r="7" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N7" s="4"/>
     </row>
-    <row r="8" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N8" s="3"/>
     </row>
-    <row r="9" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N9" s="3"/>
     </row>
-    <row r="10" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N10" s="3"/>
     </row>
-    <row r="11" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N11" s="3"/>
     </row>
-    <row r="12" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N12" s="3"/>
     </row>
-    <row r="13" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N13" s="3"/>
     </row>
-    <row r="14" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N14" s="3"/>
     </row>
-    <row r="15" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N15" s="5"/>
     </row>
-    <row r="16" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N16" s="3"/>
     </row>
-    <row r="17" spans="14:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="14:14" x14ac:dyDescent="0.45">
       <c r="N17" s="6"/>
     </row>
   </sheetData>
